--- a/Equity/output/daily/SwingStocks_Mon_19th Oct.xlsx
+++ b/Equity/output/daily/SwingStocks_Mon_19th Oct.xlsx
@@ -565,14 +565,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: NEUTRAL | Generated: 17-Oct-2026 13:29 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: NEUTRAL | Generated: 17-Oct-2026 13:50 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>WARNING: Yahoo gave no fundamentals / results dates today, so those were NOT checked - look up each stock's results date yourself before buying.   Checks: BUY ZONE now | no Risk Flags | Fundamental not Mixed | Hist Hit 7% &gt;= 25 | one stock per sector | best Hist Hit 7% first | at most 5 stocks.  At 9:15 buy only if the price is still inside Entry Low - Entry High; if it opens above, skip it.</t>
+          <t>Checks: BUY ZONE now | no Risk Flags | Fundamental not Mixed | Hist Hit 7% &gt;= 25 | one stock per sector | best Hist Hit 7% first | at most 5 stocks.  At 9:15 buy only if the price is still inside Entry Low - Entry High; if it opens above, skip it.</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         <v>13</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>3</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="T5" s="6" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>102</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>13</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="T6" s="6" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: NEUTRAL | Generated: 17-Oct-2026 13:29 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: NEUTRAL | Generated: 17-Oct-2026 13:50 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>71.27322343616365</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>20.75038304203383</v>
+        <v>20.75038304203368</v>
       </c>
       <c r="AA5" s="8" t="n">
         <v>3.734660740583819</v>
@@ -1765,7 +1765,7 @@
       <c r="AG5" s="6" t="inlineStr"/>
       <c r="AH5" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI5" s="7" t="inlineStr">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       <c r="AG6" s="6" t="inlineStr"/>
       <c r="AH6" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI6" s="7" t="inlineStr">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       <c r="AG7" s="6" t="inlineStr"/>
       <c r="AH7" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI7" s="7" t="inlineStr">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -2154,10 +2154,14 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AG8" s="6" t="inlineStr"/>
+      <c r="AG8" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
       <c r="AH8" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI8" s="7" t="inlineStr">
@@ -2211,7 +2215,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -2292,10 +2296,14 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AG9" s="6" t="inlineStr"/>
+      <c r="AG9" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="AH9" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI9" s="7" t="inlineStr">
@@ -2341,7 +2349,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -2425,7 +2433,7 @@
       <c r="AG10" s="6" t="inlineStr"/>
       <c r="AH10" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI10" s="7" t="inlineStr">
@@ -2440,7 +2448,7 @@
       </c>
       <c r="AK10" s="7" t="inlineStr">
         <is>
-          <t>[13 Oct 2026] Oriental Hotels promoter confirms no share encumbrance in FY26 - scanx.trade | [15 Oct 2026] IHCL and Oriental Hotels Announce Merger Deal - https://safariindia.com/ | [16 Oct 2026] Oriental Hotels (ORIENTHOT.NS) Climbs 4.27% to ₹151.80 as Hospitality Stock Nears Resistance - Volume Gap - https://www.siam.in/ | [11 Oct 2026] Indian Hotels (BSE:500850) - Stock Analysis - Simply Wall Street</t>
+          <t>[13 Oct 2026] Oriental Hotels promoter confirms no share encumbrance in FY26 - scanx.trade | [16 Oct 2026] Oriental Hotels (ORIENTHOT.NS) Climbs 4.27% to ₹151.80 as Hospitality Stock Nears Resistance - Volume Gap - https://www.siam.in/ | [15 Oct 2026] IHCL and Oriental Hotels Announce Merger Deal - https://safariindia.com/ | [11 Oct 2026] Indian Hotels (BSE:500850) - Stock Analysis - Simply Wall Street</t>
         </is>
       </c>
       <c r="AL10" s="10" t="inlineStr">
@@ -2479,7 +2487,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -2499,10 +2507,10 @@
         <v>1210.485</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>1131.913859465078</v>
+        <v>1131.913859162822</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>5.555789781804101</v>
+        <v>5.555789807023589</v>
       </c>
       <c r="O11" s="9" t="n">
         <v>1282.395</v>
@@ -2511,10 +2519,10 @@
         <v>1318.35</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>1.259946879726419</v>
+        <v>1.259946874007121</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>1.799924113894886</v>
+        <v>1.799924105724461</v>
       </c>
       <c r="S11" s="5" t="n">
         <v>15</v>
@@ -2535,13 +2543,13 @@
         <v>1.586297030055078</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>74.30427637137547</v>
+        <v>74.30427558647924</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>20.13124034134543</v>
+        <v>20.13123882223714</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>3.08654987878006</v>
+        <v>3.08654989279088</v>
       </c>
       <c r="AB11" s="8" t="n">
         <v>14.36068702290076</v>
@@ -2563,7 +2571,7 @@
       <c r="AG11" s="6" t="inlineStr"/>
       <c r="AH11" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI11" s="7" t="inlineStr">
@@ -2617,7 +2625,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -2701,7 +2709,7 @@
       <c r="AG12" s="6" t="inlineStr"/>
       <c r="AH12" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI12" s="7" t="inlineStr">
@@ -2751,7 +2759,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -2835,7 +2843,7 @@
       <c r="AG13" s="6" t="inlineStr"/>
       <c r="AH13" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI13" s="7" t="inlineStr">
@@ -2846,7 +2854,7 @@
       <c r="AJ13" s="7" t="inlineStr"/>
       <c r="AK13" s="7" t="inlineStr">
         <is>
-          <t>[16 Oct 2026] Aurum PropTech Posts ₹4.5 Crore Q2 Net Profit, Confirms Fund Utilisation - Sahi | [16 Oct 2026] Earnings call transcript: Aurum PropTech posts Q2 2027 profit as Housing.com deal reshapes outlook - Investing.com India | [16 Oct 2026] Aurum PropTech Q2FY27 net profit turns positive at ₹4.29 crore - scanx.trade | [16 Oct 2026] Aurum PropTech Limited Reports Earnings Results for the Second Quarter and Six Months Ended September 30, 2026 - www.marketscreener.com</t>
+          <t>[16 Oct 2026] Aurum PropTech Posts ₹4.5 Crore Q2 Net Profit, Confirms Fund Utilisation - Sahi | [16 Oct 2026] Earnings call transcript: Aurum PropTech posts Q2 2027 profit as Housing.com deal reshapes outlook - Investing.com India | [16 Oct 2026] Aurum PropTech Limited Reports Earnings Results for the Second Quarter and Six Months Ended September 30, 2026 - www.marketscreener.com | [16 Oct 2026] Aurum PropTech Q2FY27 net profit turns positive at ₹4.29 crore - scanx.trade</t>
         </is>
       </c>
       <c r="AL13" s="10" t="inlineStr">
@@ -2881,7 +2889,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -2961,7 +2969,7 @@
       <c r="AG14" s="6" t="inlineStr"/>
       <c r="AH14" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI14" s="7" t="inlineStr">
@@ -3011,7 +3019,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -3095,7 +3103,7 @@
       <c r="AG15" s="6" t="inlineStr"/>
       <c r="AH15" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI15" s="7" t="inlineStr">
@@ -3149,7 +3157,7 @@
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -3233,7 +3241,7 @@
       <c r="AG16" s="6" t="inlineStr"/>
       <c r="AH16" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI16" s="7" t="inlineStr">
@@ -3287,7 +3295,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -3346,7 +3354,7 @@
         <v>66.88693298468556</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>21.60310896302366</v>
+        <v>21.60310896302359</v>
       </c>
       <c r="AA17" s="8" t="n">
         <v>3.300886398441202</v>
@@ -3371,7 +3379,7 @@
       <c r="AG17" s="6" t="inlineStr"/>
       <c r="AH17" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI17" s="7" t="inlineStr">
@@ -3421,7 +3429,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
@@ -3505,7 +3513,7 @@
       <c r="AG18" s="6" t="inlineStr"/>
       <c r="AH18" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI18" s="7" t="inlineStr">
@@ -3559,7 +3567,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -3579,10 +3587,10 @@
         <v>5038.89</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>4789.484727829653</v>
+        <v>4789.484727828971</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>3.999103471043237</v>
+        <v>3.999103471056909</v>
       </c>
       <c r="O19" s="9" t="n">
         <v>5338.23</v>
@@ -3591,10 +3599,10 @@
         <v>5487.900000000001</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>1.750392319350001</v>
+        <v>1.750392319344016</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>2.500560456214286</v>
+        <v>2.500560456205737</v>
       </c>
       <c r="S19" s="5" t="n">
         <v>4</v>
@@ -3615,13 +3623,13 @@
         <v>1.397115867530088</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>60.50147794142603</v>
+        <v>60.50147794130429</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>15.79813209030593</v>
+        <v>15.79813208845606</v>
       </c>
       <c r="AA19" s="8" t="n">
-        <v>2.221724150579576</v>
+        <v>2.221724150587171</v>
       </c>
       <c r="AB19" s="8" t="n">
         <v>6.24840055034066</v>
@@ -3640,10 +3648,14 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AG19" s="6" t="inlineStr"/>
+      <c r="AG19" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
       <c r="AH19" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI19" s="7" t="inlineStr">
@@ -3772,7 +3784,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: NEUTRAL | Generated: 17-Oct-2026 13:29 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: NEUTRAL | Generated: 17-Oct-2026 13:50 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -3994,7 +4006,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
@@ -4074,7 +4086,7 @@
       <c r="AG5" s="6" t="inlineStr"/>
       <c r="AH5" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI5" s="7" t="inlineStr">
@@ -4120,7 +4132,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
@@ -4176,13 +4188,13 @@
         <v>1.59901391623494</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>65.74727172695339</v>
+        <v>65.74727172697395</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>26.59906531119446</v>
+        <v>26.59906531042339</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>5.162501685855343</v>
+        <v>5.162501685856903</v>
       </c>
       <c r="AB6" s="8" t="n">
         <v>11.38876635832151</v>
@@ -4204,7 +4216,7 @@
       <c r="AG6" s="6" t="inlineStr"/>
       <c r="AH6" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI6" s="7" t="inlineStr">
@@ -4254,7 +4266,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -4338,7 +4350,7 @@
       <c r="AG7" s="6" t="inlineStr"/>
       <c r="AH7" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI7" s="7" t="inlineStr">
@@ -4388,7 +4400,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -4472,7 +4484,7 @@
       <c r="AG8" s="6" t="inlineStr"/>
       <c r="AH8" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI8" s="7" t="inlineStr">
@@ -4518,7 +4530,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -4602,7 +4614,7 @@
       <c r="AG9" s="6" t="inlineStr"/>
       <c r="AH9" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI9" s="7" t="inlineStr">
@@ -4656,7 +4668,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -4676,10 +4688,10 @@
         <v>1393.8</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>1308.933030522079</v>
+        <v>1308.933030474585</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>5.149780396950815</v>
+        <v>5.149780400392396</v>
       </c>
       <c r="O10" s="9" t="n">
         <v>1476.6</v>
@@ -4688,10 +4700,10 @@
         <v>1518</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>1.359281262584461</v>
+        <v>1.359281261676058</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>1.941830375120659</v>
+        <v>1.94183037382294</v>
       </c>
       <c r="S10" s="5" t="n">
         <v>14</v>
@@ -4712,13 +4724,13 @@
         <v>1.546948642665332</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>70.16445404447384</v>
+        <v>70.16445417213112</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>21.39035122212736</v>
+        <v>21.39035001172544</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>2.860989109417116</v>
+        <v>2.860989111329113</v>
       </c>
       <c r="AB10" s="8" t="n">
         <v>11.11611296474564</v>
@@ -4730,17 +4742,21 @@
         <v>11.42385028450349</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>-19.47495052488568</v>
+        <v>-19.47495654757913</v>
       </c>
       <c r="AF10" s="6" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AG10" s="6" t="inlineStr"/>
+      <c r="AG10" s="6" t="inlineStr">
+        <is>
+          <t>2027-01-11</t>
+        </is>
+      </c>
       <c r="AH10" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI10" s="7" t="inlineStr">
@@ -4794,7 +4810,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -4878,7 +4894,7 @@
       <c r="AG11" s="6" t="inlineStr"/>
       <c r="AH11" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI11" s="7" t="inlineStr">
@@ -4908,17 +4924,17 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Nazara Technologies Limited</t>
+          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -4928,11 +4944,11 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - above entry zone, don't chase</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -4940,73 +4956,73 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>418.1499938964844</v>
+        <v>596.5</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>418.1499938964844</v>
+        <v>616.3</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>413.9684939575195</v>
+        <v>590.535</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>422.3314938354492</v>
+        <v>602.465</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>393.5134938283118</v>
+        <v>557.7275000000001</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>5.89178534683214</v>
+        <v>6.499999999999988</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>447.4204934692383</v>
+        <v>638.255</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>459.9649932861328</v>
+        <v>656.1500000000001</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>1.188094879214111</v>
+        <v>1.076923076923079</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>1.697278398877302</v>
+        <v>1.538461538461544</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>16725.99975585938</v>
+        <v>14912.5</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>46.66666666666666</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>30.66666666666666</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>0.9869207715361562</v>
+        <v>8.266304109774618</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>73.72559863121177</v>
+        <v>62.29406094460268</v>
       </c>
       <c r="Z12" s="8" t="n">
-        <v>35.3737148672471</v>
+        <v>38.67790500869441</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>3.273214081573411</v>
+        <v>4.571139626664222</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>19.08016550322109</v>
+        <v>14.17360246201409</v>
       </c>
       <c r="AC12" s="8" t="n">
-        <v>37.25586813521016</v>
+        <v>22.92632663575476</v>
       </c>
       <c r="AD12" s="8" t="n">
-        <v>19.38790282297894</v>
+        <v>14.48133978177194</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>-0.4167659027000226</v>
+        <v>-8.287211314701349</v>
       </c>
       <c r="AF12" s="6" t="inlineStr">
         <is>
@@ -5016,22 +5032,18 @@
       <c r="AG12" s="6" t="inlineStr"/>
       <c r="AH12" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI12" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Closed above prior 20D high | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 47% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ12" s="7" t="inlineStr">
-        <is>
-          <t>RSI&gt;70 (hot) | Extended &gt;7% above EMA20 | Volume below average</t>
-        </is>
-      </c>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 8.3x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 55% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ12" s="7" t="inlineStr"/>
       <c r="AK12" s="7" t="inlineStr">
         <is>
-          <t>[13 Oct 2026] Motilal Oswal, Nazara Tech and 3 Other Stocks Trading Near Their Resistance Zones - Trade Brains | [12 Oct 2026] Nazara Technologies approves $77 million investment in UK subsidiary amidst leadership changes - Business Upturn | [12 Oct 2026] Nazara Technologies approves USD 77 million investment in UK subsidiary and announces leadership changes - Business Upturn</t>
+          <t>[17 Oct 2026] Results: Leela Palaces Hotels &amp; Resorts Limited Beat Earnings Expectations And Analysts Now Have New Forecasts - Simply Wall Street | [16 Oct 2026] LEELA PALACES HOTEL LTD Share Price - Live NSE: THELEELA Stock Price &amp; Chart - Upstox | [14 Oct 2026] Leela Palaces Hotels &amp; Resorts Limited Reports Earnings Results for the Second Quarter and Six Months Ended September 30, 2026 - www.marketscreener.com | [14 Oct 2026] Leela Palaces Hotels to host investor meetings in Singapore on Oct 19-20 - scanx.trade</t>
         </is>
       </c>
       <c r="AL12" s="10" t="inlineStr">
@@ -5046,19 +5058,15 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>WSTCSTPAPR</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Consumer Services</t>
-        </is>
-      </c>
+          <t>West Coast Paper Mills Limited</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="6" t="inlineStr">
         <is>
           <t>TREND CONTINUATION</t>
@@ -5070,7 +5078,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -5078,73 +5086,73 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>596.5</v>
+        <v>822.4000244140625</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>616.3</v>
+        <v>840</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>590.535</v>
+        <v>814.1760241699219</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>602.465</v>
+        <v>830.6240246582031</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>557.7275000000001</v>
+        <v>768.9440228271485</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>6.499999999999988</v>
+        <v>6.499999999999992</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>638.255</v>
+        <v>879.9680261230469</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>656.1500000000001</v>
+        <v>904.6400268554688</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>1.076923076923079</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>1.538461538461544</v>
+        <v>1.538461538461542</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>14912.5</v>
+        <v>14803.20043945312</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>54.54545454545454</v>
+        <v>70.27027027027027</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>36.36363636363637</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="W13" s="5" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="X13" s="8" t="n">
-        <v>8.266304109774618</v>
+        <v>1.70697963357593</v>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>62.29406094460268</v>
+        <v>57.54259144072577</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>38.67790500869441</v>
+        <v>43.40740447414429</v>
       </c>
       <c r="AA13" s="8" t="n">
-        <v>4.571139626664222</v>
+        <v>6.669599061534069</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>14.17360246201409</v>
+        <v>15.29511264379264</v>
       </c>
       <c r="AC13" s="8" t="n">
-        <v>22.92632663575476</v>
+        <v>57.06202598117125</v>
       </c>
       <c r="AD13" s="8" t="n">
-        <v>14.48133978177194</v>
+        <v>15.60284996355049</v>
       </c>
       <c r="AE13" s="8" t="n">
-        <v>-8.287211314701349</v>
+        <v>-15.9143157631585</v>
       </c>
       <c r="AF13" s="6" t="inlineStr">
         <is>
@@ -5154,18 +5162,22 @@
       <c r="AG13" s="6" t="inlineStr"/>
       <c r="AH13" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI13" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 8.3x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 55% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ13" s="7" t="inlineStr"/>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.7x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 70% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ13" s="7" t="inlineStr">
+        <is>
+          <t>RELAXED smallcap</t>
+        </is>
+      </c>
       <c r="AK13" s="7" t="inlineStr">
         <is>
-          <t>[17 Oct 2026] Results: Leela Palaces Hotels &amp; Resorts Limited Beat Earnings Expectations And Analysts Now Have New Forecasts - Simply Wall Street | [16 Oct 2026] LEELA PALACES HOTEL LTD Share Price - Live NSE: THELEELA Stock Price &amp; Chart - Upstox | [14 Oct 2026] Leela Palaces Hotels &amp; Resorts Limited Reports Earnings Results for the Second Quarter and Six Months Ended September 30, 2026 - www.marketscreener.com | [14 Oct 2026] Leela Palaces Hotels to host investor meetings in Singapore on Oct 19-20 - scanx.trade</t>
+          <t>[16 Oct 2026] West Coast Paper Mills (NSE:WSTCSTPAPR): What Triggered the Price Movement Clarification? - Kalkine India | [16 Oct 2026] West Coast Paper Mills clarifies on security price movement - Business Upturn | [14 Oct 2026] Havells India and 6 Other Stocks in Which SBI Group Bought Fresh Stakes Worth ₹2,297 Cr in Q2 FY27 - Trade Brains</t>
         </is>
       </c>
       <c r="AL13" s="10" t="inlineStr">
@@ -5180,27 +5192,31 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TEXINFRA</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Texmaco Infrastructure &amp; Holdings Limited</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr"/>
+          <t>Nazara Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Media Entertainment &amp; Publication</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>WAIT - above entry zone, don't chase</t>
+          <t>BUY ZONE</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -5208,73 +5224,73 @@
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>123.9800033569336</v>
+        <v>418.1499938964844</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>128.14</v>
+        <v>418.1499938964844</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>122.7402033233643</v>
+        <v>413.9684939575195</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>125.2198033905029</v>
+        <v>422.3314938354492</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>115.9213031387329</v>
+        <v>393.5134938283118</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>6.499999999999989</v>
+        <v>5.89178534683214</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>132.658603591919</v>
+        <v>447.4204934692383</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>136.378003692627</v>
+        <v>459.9649932861328</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>1.076923076923081</v>
+        <v>1.188094879214111</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>1.538461538461544</v>
+        <v>1.697278398877302</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>15373.52041625977</v>
+        <v>16725.99975585938</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>47.22222222222222</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>30.55555555555556</v>
+        <v>30.66666666666666</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>1.393805643299728</v>
+        <v>0.9869207715361562</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>59.47946329370782</v>
+        <v>73.72559863121177</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>26.3544226690262</v>
+        <v>35.3737148672471</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>4.282590042824988</v>
+        <v>3.273214081573411</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>8.687651169125953</v>
+        <v>19.08016550322109</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>8.91550755946473</v>
+        <v>37.25586813521016</v>
       </c>
       <c r="AD14" s="8" t="n">
-        <v>8.995388488883803</v>
+        <v>19.38790282297894</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>-3.854202178309041</v>
+        <v>-0.4167659027000226</v>
       </c>
       <c r="AF14" s="6" t="inlineStr">
         <is>
@@ -5284,18 +5300,22 @@
       <c r="AG14" s="6" t="inlineStr"/>
       <c r="AH14" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="AI14" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.4x avg | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 47% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ14" s="7" t="inlineStr"/>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Closed above prior 20D high | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 47% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ14" s="7" t="inlineStr">
+        <is>
+          <t>RSI&gt;70 (hot) | Extended &gt;7% above EMA20 | Volume below average</t>
+        </is>
+      </c>
       <c r="AK14" s="7" t="inlineStr">
         <is>
-          <t>[14 Oct 2026] Texmaco Infrastructure &amp; Holdings Limited (TEXINFRA.BO) - Yahoo! Finance Canada</t>
+          <t>[13 Oct 2026] Motilal Oswal, Nazara Tech and 3 Other Stocks Trading Near Their Resistance Zones - Trade Brains | [12 Oct 2026] Nazara Technologies approves $77 million investment in UK subsidiary amidst leadership changes - Business Upturn | [12 Oct 2026] Nazara Technologies approves USD 77 million investment in UK subsidiary and announces leadership changes - Business Upturn</t>
         </is>
       </c>
       <c r="AL14" s="10" t="inlineStr">
@@ -5310,27 +5330,27 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>WSTCSTPAPR</t>
+          <t>AVTNPL</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>West Coast Paper Mills Limited</t>
+          <t>AVT Natural Products Limited</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>WAIT - above entry zone, don't chase</t>
+          <t>BUY ZONE</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -5338,73 +5358,73 @@
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>822.4000244140625</v>
+        <v>99.75</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>840</v>
+        <v>101</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>814.1760241699219</v>
+        <v>98.7525</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>830.6240246582031</v>
+        <v>100.7475</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>768.9440228271485</v>
+        <v>93.26625</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>6.499999999999992</v>
+        <v>6.5</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>879.9680261230469</v>
+        <v>106.7325</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>904.6400268554688</v>
+        <v>109.725</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>1.076923076923079</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.53846153846154</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>14803.20043945312</v>
+        <v>15361.5</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>70.27027027027027</v>
+        <v>50</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>40.54054054054054</v>
+        <v>45</v>
       </c>
       <c r="W15" s="5" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="X15" s="8" t="n">
-        <v>1.70697963357593</v>
+        <v>1.48474111643167</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>57.54259144072577</v>
+        <v>63.0830508635324</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>43.40740447414429</v>
+        <v>25.834372514938</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>6.669599061534069</v>
+        <v>5.843606873783505</v>
       </c>
       <c r="AB15" s="8" t="n">
-        <v>15.29511264379264</v>
+        <v>15.66558728070908</v>
       </c>
       <c r="AC15" s="8" t="n">
-        <v>57.06202598117125</v>
+        <v>42.76573761716853</v>
       </c>
       <c r="AD15" s="8" t="n">
-        <v>15.60284996355049</v>
+        <v>15.97332460046693</v>
       </c>
       <c r="AE15" s="8" t="n">
-        <v>-15.9143157631585</v>
+        <v>-5.29763764744332</v>
       </c>
       <c r="AF15" s="6" t="inlineStr">
         <is>
@@ -5414,12 +5434,12 @@
       <c r="AG15" s="6" t="inlineStr"/>
       <c r="AH15" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI15" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.7x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 70% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.5x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 50% of similar setups</t>
         </is>
       </c>
       <c r="AJ15" s="7" t="inlineStr">
@@ -5429,7 +5449,7 @@
       </c>
       <c r="AK15" s="7" t="inlineStr">
         <is>
-          <t>[16 Oct 2026] West Coast Paper Mills (NSE:WSTCSTPAPR): What Triggered the Price Movement Clarification? - Kalkine India | [16 Oct 2026] West Coast Paper Mills clarifies on security price movement - Business Upturn | [14 Oct 2026] Havells India and 6 Other Stocks in Which SBI Group Bought Fresh Stakes Worth ₹2,297 Cr in Q2 FY27 - Trade Brains</t>
+          <t>[12 Oct 2026] AVT Natural Products NSE:AVTNPL Volume Spurt Clarification - Kalkine India</t>
         </is>
       </c>
       <c r="AL15" s="10" t="inlineStr">
@@ -5444,27 +5464,27 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>AVTNPL</t>
+          <t>SVLL</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>AVT Natural Products Limited</t>
+          <t>Shree Vasu Logistics Limited</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - above entry zone, don't chase</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -5472,88 +5492,84 @@
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>99.75</v>
+        <v>867.9500122070312</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>101</v>
+        <v>881.45</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>98.7525</v>
+        <v>859.270512084961</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>100.7475</v>
+        <v>876.6295123291015</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>93.26625</v>
+        <v>811.5332614135742</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>6.5</v>
+        <v>6.499999999999999</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>106.7325</v>
+        <v>928.7065130615235</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>109.725</v>
+        <v>954.7450134277344</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>1.076923076923077</v>
+        <v>1.076923076923079</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>1.53846153846154</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>15361.5</v>
+        <v>14755.15020751953</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>50</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>45</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="W16" s="5" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="X16" s="8" t="n">
-        <v>1.48474111643167</v>
+        <v>1.06633174331509</v>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>63.0830508635324</v>
+        <v>63.18625963412578</v>
       </c>
       <c r="Z16" s="8" t="n">
-        <v>25.83437251493751</v>
+        <v>27.81163412787848</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>5.843606873783505</v>
+        <v>4.774286869448234</v>
       </c>
       <c r="AB16" s="8" t="n">
-        <v>15.66558728070908</v>
+        <v>9.811486006779656</v>
       </c>
       <c r="AC16" s="8" t="n">
-        <v>42.76573761716853</v>
+        <v>22.27231697663889</v>
       </c>
       <c r="AD16" s="8" t="n">
-        <v>15.97332460046693</v>
+        <v>10.11922332653751</v>
       </c>
       <c r="AE16" s="8" t="n">
-        <v>-5.29763764744332</v>
-      </c>
-      <c r="AF16" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-3.287091158141819</v>
+      </c>
+      <c r="AF16" s="6" t="inlineStr"/>
       <c r="AG16" s="6" t="inlineStr"/>
       <c r="AH16" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI16" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.5x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 50% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 47% of similar setups</t>
         </is>
       </c>
       <c r="AJ16" s="7" t="inlineStr">
@@ -5561,11 +5577,7 @@
           <t>RELAXED smallcap</t>
         </is>
       </c>
-      <c r="AK16" s="7" t="inlineStr">
-        <is>
-          <t>[12 Oct 2026] AVT Natural Products NSE:AVTNPL Volume Spurt Clarification - Kalkine India</t>
-        </is>
-      </c>
+      <c r="AK16" s="7" t="inlineStr"/>
       <c r="AL16" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -5578,12 +5590,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>MAGADSUGAR</t>
+          <t>TEXINFRA</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Magadh Sugar &amp; Energy Limited</t>
+          <t>Texmaco Infrastructure &amp; Holdings Limited</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
@@ -5594,11 +5606,11 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - above entry zone, don't chase</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -5606,73 +5618,73 @@
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>602.1500244140625</v>
+        <v>123.9800033569336</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>602.1500244140625</v>
+        <v>128.14</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>596.1285241699219</v>
+        <v>122.7402033233643</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>608.1715246582031</v>
+        <v>125.2198033905029</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>563.0102728271485</v>
+        <v>115.9213031387329</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>6.499999999999995</v>
+        <v>6.499999999999989</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>644.3005261230469</v>
+        <v>132.658603591919</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>662.3650268554688</v>
+        <v>136.378003692627</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>1.076923076923078</v>
+        <v>1.076923076923081</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.538461538461544</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>15053.75061035156</v>
+        <v>15373.52041625977</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>36.36363636363637</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>27.27272727272727</v>
+        <v>30.55555555555556</v>
       </c>
       <c r="W17" s="5" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>1.384160103984141</v>
+        <v>1.393805643299728</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>60.99702355789643</v>
+        <v>59.47946329370782</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>26.98687608624708</v>
+        <v>26.3544226690262</v>
       </c>
       <c r="AA17" s="8" t="n">
-        <v>5.119500301676951</v>
+        <v>4.282590042824988</v>
       </c>
       <c r="AB17" s="8" t="n">
-        <v>19.07257462504175</v>
+        <v>8.687651169125953</v>
       </c>
       <c r="AC17" s="8" t="n">
-        <v>20.33373936024203</v>
+        <v>8.91550755946473</v>
       </c>
       <c r="AD17" s="8" t="n">
-        <v>19.3803119447996</v>
+        <v>8.995388488883803</v>
       </c>
       <c r="AE17" s="8" t="n">
-        <v>-5.165759061718711</v>
+        <v>-3.854202178309041</v>
       </c>
       <c r="AF17" s="6" t="inlineStr">
         <is>
@@ -5682,22 +5694,18 @@
       <c r="AG17" s="6" t="inlineStr"/>
       <c r="AH17" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="AI17" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.4x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 36% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ17" s="7" t="inlineStr">
-        <is>
-          <t>Extended &gt;7% above EMA20 | High volatility</t>
-        </is>
-      </c>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.4x avg | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 47% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ17" s="7" t="inlineStr"/>
       <c r="AK17" s="7" t="inlineStr">
         <is>
-          <t>[13 Oct 2026] Magadh Sugar &amp; Energy (MAGADSUGAR.NS) Jumps 7.50% to ₹579.30 as Bulls Test ₹608 Ceiling - Quality Factor - https://www.siam.in/</t>
+          <t>[14 Oct 2026] Texmaco Infrastructure &amp; Holdings Limited (TEXINFRA.BO) - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="AL17" s="10" t="inlineStr">
@@ -5712,18 +5720,18 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>SVLL</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Shree Vasu Logistics Limited</t>
+          <t>Iris Clothings Limited</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -5732,7 +5740,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
@@ -5740,92 +5748,100 @@
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>867.9500122070312</v>
+        <v>63.13000106811523</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>881.45</v>
+        <v>64.34</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>859.270512084961</v>
+        <v>62.49870105743408</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>876.6295123291015</v>
+        <v>63.76130107879639</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>811.5332614135742</v>
+        <v>59.02655099868775</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>6.499999999999999</v>
+        <v>6.499999999999997</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>928.7065130615235</v>
+        <v>67.5491011428833</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>954.7450134277344</v>
+        <v>69.44300117492676</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>1.076923076923079</v>
+        <v>1.076923076923078</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>1.538461538461539</v>
+        <v>1.538461538461541</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>17</v>
+        <v>243</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>14755.15020751953</v>
+        <v>15340.590259552</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>47.05882352941176</v>
+        <v>75</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>33.33333333333333</v>
+        <v>60</v>
       </c>
       <c r="W18" s="5" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>1.06633174331509</v>
+        <v>2.196919835895545</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>63.18625963412578</v>
+        <v>58.43343321644641</v>
       </c>
       <c r="Z18" s="8" t="n">
-        <v>27.81163412787848</v>
+        <v>21.56575419120254</v>
       </c>
       <c r="AA18" s="8" t="n">
-        <v>4.774286869448234</v>
+        <v>5.334756382905119</v>
       </c>
       <c r="AB18" s="8" t="n">
-        <v>9.811486006779656</v>
+        <v>8.67619366894219</v>
       </c>
       <c r="AC18" s="8" t="n">
-        <v>22.27231697663889</v>
+        <v>34.83554352755374</v>
       </c>
       <c r="AD18" s="8" t="n">
-        <v>10.11922332653751</v>
+        <v>8.98393098870004</v>
       </c>
       <c r="AE18" s="8" t="n">
-        <v>-3.287091158141819</v>
-      </c>
-      <c r="AF18" s="6" t="inlineStr"/>
+        <v>-7.161763135124655</v>
+      </c>
+      <c r="AF18" s="6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AG18" s="6" t="inlineStr"/>
       <c r="AH18" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI18" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 47% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | Volume 2.2x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 75% of similar setups</t>
         </is>
       </c>
       <c r="AJ18" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
-        </is>
-      </c>
-      <c r="AK18" s="7" t="inlineStr"/>
+          <t>Big 1D spike | High volatility</t>
+        </is>
+      </c>
+      <c r="AK18" s="7" t="inlineStr">
+        <is>
+          <t>[15 Oct 2026] Iris Clothings (NSE:IRISDOREME): What Does Its Q2 FY27 Reg 74(5) Certificate Reveal? - Kalkine India</t>
+        </is>
+      </c>
       <c r="AL18" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -5838,18 +5854,18 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MAGADSUGAR</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Allcargo Terminals Limited</t>
+          <t>Magadh Sugar &amp; Energy Limited</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -5858,7 +5874,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -5866,69 +5882,73 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>28.1200008392334</v>
+        <v>602.1500244140625</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>28.1200008392334</v>
+        <v>602.1500244140625</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>27.83880083084106</v>
+        <v>596.1285241699219</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>28.40120084762573</v>
+        <v>608.1715246582031</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>26.29220078468323</v>
+        <v>563.0102728271485</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>6.499999999999999</v>
+        <v>6.499999999999995</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>30.08840089797974</v>
+        <v>644.3005261230469</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>30.93200092315674</v>
+        <v>662.3650268554688</v>
       </c>
       <c r="Q19" s="8" t="n">
         <v>1.076923076923078</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>1.538461538461541</v>
+        <v>1.538461538461542</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>547</v>
+        <v>25</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>15381.64045906067</v>
-      </c>
-      <c r="U19" s="6" t="inlineStr"/>
-      <c r="V19" s="6" t="inlineStr"/>
+        <v>15053.75061035156</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>27.27272727272727</v>
+      </c>
       <c r="W19" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>5.300273519141848</v>
+        <v>1.384160103984141</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>64.54859228508229</v>
+        <v>60.99702355789643</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>17.2021058428417</v>
+        <v>26.98687608624708</v>
       </c>
       <c r="AA19" s="8" t="n">
-        <v>5.030449084298655</v>
+        <v>5.119500301676951</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>17.70615972228875</v>
+        <v>19.07257462504175</v>
       </c>
       <c r="AC19" s="8" t="n">
-        <v>22.26087321405825</v>
+        <v>20.33373936024203</v>
       </c>
       <c r="AD19" s="8" t="n">
-        <v>18.0138970420466</v>
+        <v>19.3803119447996</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>-27.31971610921373</v>
+        <v>-5.165759061718711</v>
       </c>
       <c r="AF19" s="6" t="inlineStr">
         <is>
@@ -5938,22 +5958,22 @@
       <c r="AG19" s="6" t="inlineStr"/>
       <c r="AH19" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="AI19" s="7" t="inlineStr">
         <is>
-          <t>MACD bullish | Volume 5.3x avg | OBV rising | Closed above prior 20D high | Beating NIFTY 1M</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.4x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 36% of similar setups</t>
         </is>
       </c>
       <c r="AJ19" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>Extended &gt;7% above EMA20 | High volatility</t>
         </is>
       </c>
       <c r="AK19" s="7" t="inlineStr">
         <is>
-          <t>[16 Oct 2026] Allcargo Terminals starts e-voting to ratify ₹79 crore RPTs - scanx.trade | [13 Oct 2026] Allcargo Global Starts Trading On NSE, BSE - https://www.fintechbiznews.com/ | [14 Oct 2026] Allcargo Terminals ATL Board Ratifies Related Party Transactions - Kalkine India | [12 Oct 2026] GPPL Stock Price and Chart — NSE:GPPL - TradingView</t>
+          <t>[13 Oct 2026] Magadh Sugar &amp; Energy (MAGADSUGAR.NS) Jumps 7.50% to ₹579.30 as Bulls Test ₹608 Ceiling - Quality Factor - https://www.siam.in/</t>
         </is>
       </c>
       <c r="AL19" s="10" t="inlineStr">
@@ -5968,27 +5988,27 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Iris Clothings Limited</t>
+          <t>Creative Newtech Limited</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>WAIT - above entry zone, don't chase</t>
+          <t>WAIT - trigger not hit (buy above 1187.19)</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
@@ -5996,28 +6016,28 @@
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>63.13000106811523</v>
+        <v>1154.800048828125</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>64.34</v>
+        <v>1178.7</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>62.49870105743408</v>
+        <v>1187.186</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>63.76130107879639</v>
+        <v>1203.79</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>59.02655099868775</v>
+        <v>1117.78128</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>6.499999999999997</v>
+        <v>6.499999999999993</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>67.5491011428833</v>
+        <v>1279.17216</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>69.44300117492676</v>
+        <v>1315.0368</v>
       </c>
       <c r="Q20" s="8" t="n">
         <v>1.076923076923078</v>
@@ -6026,43 +6046,43 @@
         <v>1.538461538461541</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>243</v>
+        <v>12</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>15340.590259552</v>
+        <v>14345.856</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>75</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>60</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="W20" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>2.196919835895545</v>
+        <v>2.170612130550497</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>58.43343321644641</v>
+        <v>58.67222777648303</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>21.56575419120254</v>
+        <v>16.28024138279779</v>
       </c>
       <c r="AA20" s="8" t="n">
-        <v>5.334756382905119</v>
+        <v>4.857618751512831</v>
       </c>
       <c r="AB20" s="8" t="n">
-        <v>8.67619366894219</v>
+        <v>8.115420522990746</v>
       </c>
       <c r="AC20" s="8" t="n">
-        <v>34.83554352755374</v>
+        <v>25.92743997408537</v>
       </c>
       <c r="AD20" s="8" t="n">
-        <v>8.98393098870004</v>
+        <v>8.423157842748596</v>
       </c>
       <c r="AE20" s="8" t="n">
-        <v>-7.161763135124655</v>
+        <v>-13.00290939035256</v>
       </c>
       <c r="AF20" s="6" t="inlineStr">
         <is>
@@ -6072,22 +6092,22 @@
       <c r="AG20" s="6" t="inlineStr"/>
       <c r="AH20" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI20" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | Volume 2.2x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 75% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 2.2x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 42% of similar setups</t>
         </is>
       </c>
       <c r="AJ20" s="7" t="inlineStr">
         <is>
-          <t>Big 1D spike | High volatility</t>
+          <t>RELAXED smallcap</t>
         </is>
       </c>
       <c r="AK20" s="7" t="inlineStr">
         <is>
-          <t>[15 Oct 2026] Iris Clothings (NSE:IRISDOREME): What Does Its Q2 FY27 Reg 74(5) Certificate Reveal? - Kalkine India</t>
+          <t>[14 Oct 2026] Creative Newtech (CNL.NS) Climbs 2.90% to ₹1,086.1 as Stock Holds Above Key Support - Collar Trade - https://www.siam.in/</t>
         </is>
       </c>
       <c r="AL20" s="10" t="inlineStr">
@@ -6102,15 +6122,19 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Creative Newtech Limited</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr"/>
+          <t>Coforge Limited</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
           <t>NEAR BREAKOUT</t>
@@ -6118,11 +6142,11 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>WAIT - trigger not hit (buy above 1187.19)</t>
+          <t>WAIT - trigger not hit (buy above 1971.97)</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -6130,98 +6154,102 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1154.800048828125</v>
+        <v>1951.900024414062</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1178.7</v>
+        <v>1951.900024414062</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1187.186</v>
+        <v>1971.97</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1203.79</v>
+        <v>1999.55</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>1117.78128</v>
+        <v>1878.064063120127</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>6.499999999999993</v>
+        <v>5.423411534116526</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>1279.17216</v>
+        <v>2124.7632</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1315.0368</v>
+        <v>2184.336</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>1.076923076923078</v>
+        <v>1.29070050391083</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>1.538461538461541</v>
+        <v>1.843857862729756</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>14345.856</v>
+        <v>17871.84</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>41.66666666666667</v>
+        <v>34.14634146341464</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>33.33333333333333</v>
+        <v>7.317073170731707</v>
       </c>
       <c r="W21" s="5" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="X21" s="8" t="n">
-        <v>2.170612130550497</v>
+        <v>1.007088666597277</v>
       </c>
       <c r="Y21" s="8" t="n">
-        <v>58.67222777648303</v>
+        <v>64.31412123403931</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>16.28024138279779</v>
+        <v>19.68999862120563</v>
       </c>
       <c r="AA21" s="8" t="n">
-        <v>4.857618751512831</v>
+        <v>3.065273594754632</v>
       </c>
       <c r="AB21" s="8" t="n">
-        <v>8.115420522990746</v>
+        <v>10.4828255142783</v>
       </c>
       <c r="AC21" s="8" t="n">
-        <v>25.92743997408537</v>
+        <v>29.70347481966595</v>
       </c>
       <c r="AD21" s="8" t="n">
-        <v>8.423157842748596</v>
+        <v>10.79056283403615</v>
       </c>
       <c r="AE21" s="8" t="n">
-        <v>-13.00290939035256</v>
+        <v>-3.428652702946733</v>
       </c>
       <c r="AF21" s="6" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AG21" s="6" t="inlineStr"/>
+      <c r="AG21" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="AH21" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI21" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 2.2x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 42% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 34% of similar setups</t>
         </is>
       </c>
       <c r="AJ21" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>Weak trend (ADX&lt;20)</t>
         </is>
       </c>
       <c r="AK21" s="7" t="inlineStr">
         <is>
-          <t>[14 Oct 2026] Creative Newtech (CNL.NS) Climbs 2.90% to ₹1,086.1 as Stock Holds Above Key Support - Collar Trade - https://www.siam.in/</t>
+          <t>[14 Oct 2026] Coforge Share Price - Upstox | [14 Oct 2026] Coforge completes allotment of 1.26 crore shares for Cigniti merger - scanx.trade | [12 Oct 2026] Coforge Limited (COFORGE.NS) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada | [14 Oct 2026] Coforge NSE:COFORGE Regulation 74(5) Certificate Q2 FY27 - Kalkine India</t>
         </is>
       </c>
       <c r="AL21" s="10" t="inlineStr">
@@ -6236,31 +6264,31 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Coforge Limited</t>
+          <t>Aditya Infotech Limited</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>WAIT - trigger not hit (buy above 1971.97)</t>
+          <t>BUY ZONE</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -6268,73 +6296,73 @@
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1951.900024414062</v>
+        <v>4109.10009765625</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1951.900024414062</v>
+        <v>4063.6</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>1971.97</v>
+        <v>4068.009096679687</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1999.55</v>
+        <v>4150.191098632812</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>1878.064063120127</v>
+        <v>3842.008591308594</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>5.423411534116548</v>
+        <v>6.499999999999992</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>2124.7632</v>
+        <v>4396.737104492187</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>2184.336</v>
+        <v>4520.010107421876</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.290700503910824</v>
+        <v>1.076923076923078</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>1.843857862729748</v>
+        <v>1.538461538461542</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>17871.84</v>
+        <v>12327.30029296875</v>
       </c>
       <c r="U22" s="8" t="n">
-        <v>34.14634146341464</v>
+        <v>69.38775510204081</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>7.317073170731707</v>
+        <v>53.06122448979592</v>
       </c>
       <c r="W22" s="5" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>1.007088666597277</v>
+        <v>1.65057826971186</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>64.31412123403905</v>
+        <v>56.59143028579934</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>19.68999862119611</v>
+        <v>27.25678942630232</v>
       </c>
       <c r="AA22" s="8" t="n">
-        <v>3.065273594754645</v>
+        <v>5.530016159127127</v>
       </c>
       <c r="AB22" s="8" t="n">
-        <v>10.4828255142783</v>
+        <v>12.16629926280646</v>
       </c>
       <c r="AC22" s="8" t="n">
-        <v>29.70347481966595</v>
+        <v>8.183304551298164</v>
       </c>
       <c r="AD22" s="8" t="n">
-        <v>10.79056283403615</v>
+        <v>12.47403658256431</v>
       </c>
       <c r="AE22" s="8" t="n">
-        <v>-3.428652702946733</v>
+        <v>-11.05843944466991</v>
       </c>
       <c r="AF22" s="6" t="inlineStr">
         <is>
@@ -6344,22 +6372,22 @@
       <c r="AG22" s="6" t="inlineStr"/>
       <c r="AH22" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI22" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 34% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.7x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 69% of similar setups</t>
         </is>
       </c>
       <c r="AJ22" s="7" t="inlineStr">
         <is>
-          <t>Weak trend (ADX&lt;20)</t>
+          <t>High volatility</t>
         </is>
       </c>
       <c r="AK22" s="7" t="inlineStr">
         <is>
-          <t>[14 Oct 2026] Coforge Share Price - Upstox | [14 Oct 2026] Coforge completes allotment of 1.26 crore shares for Cigniti merger - scanx.trade | [12 Oct 2026] Coforge Limited (COFORGE.NS) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada | [14 Oct 2026] Coforge NSE:COFORGE Regulation 74(5) Certificate Q2 FY27 - Kalkine India</t>
+          <t>[14 Oct 2026] Aditya Infotech (NSEI:CPPLUS) Stock Forecast &amp; Analyst Predictions - Simply Wall Street | [14 Oct 2026] CPPLUS Share Price Near 52-Week High: Key Stock Analysis - Univest | [14 Oct 2026] Aditya Infotech (NSE:CPPLUS): What Does the Q2 FY27 Share Capital Audit Show? - Kalkine India | [15 Oct 2026] Dynamic Services &amp; Security Share Price today at Rs 130 - Univest</t>
         </is>
       </c>
       <c r="AL22" s="10" t="inlineStr">
@@ -6374,22 +6402,22 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Aditya Infotech Limited</t>
+          <t>Just Dial Limited</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -6398,7 +6426,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
@@ -6406,100 +6434,88 @@
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>4109.10009765625</v>
+        <v>713.25</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>4063.6</v>
+        <v>713.25</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>4068.009096679687</v>
+        <v>706.1174999999999</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>4150.191098632812</v>
+        <v>720.3825000000001</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>3842.008591308594</v>
+        <v>673.1319549905328</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>6.499999999999992</v>
+        <v>5.624682090356426</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>4396.737104492187</v>
+        <v>763.1775</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>4520.010107421876</v>
+        <v>784.575</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>1.076923076923078</v>
+        <v>1.244514781022304</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.777878258603292</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>12327.30029296875</v>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v>69.38775510204081</v>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v>53.06122448979592</v>
-      </c>
+        <v>17118</v>
+      </c>
+      <c r="U23" s="6" t="inlineStr"/>
+      <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="5" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="X23" s="8" t="n">
-        <v>1.65057826971186</v>
+        <v>4.913118796071611</v>
       </c>
       <c r="Y23" s="8" t="n">
-        <v>56.59143028579934</v>
+        <v>64.37933294993516</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>27.25678942630232</v>
+        <v>14.89965877420833</v>
       </c>
       <c r="AA23" s="8" t="n">
-        <v>5.530016159127127</v>
+        <v>3.124823383531349</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>12.16629926280646</v>
+        <v>5.870563615310553</v>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>8.183304551298164</v>
+        <v>-7.044179415203167</v>
       </c>
       <c r="AD23" s="8" t="n">
-        <v>12.47403658256431</v>
+        <v>6.178300935068403</v>
       </c>
       <c r="AE23" s="8" t="n">
-        <v>-11.05843944466991</v>
-      </c>
-      <c r="AF23" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-18.81971092426513</v>
+      </c>
+      <c r="AF23" s="6" t="inlineStr"/>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI23" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.7x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 69% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 4.9x avg | OBV rising | Closed above prior 20D high | Beating NIFTY 1M</t>
         </is>
       </c>
       <c r="AJ23" s="7" t="inlineStr">
         <is>
-          <t>High volatility</t>
-        </is>
-      </c>
-      <c r="AK23" s="7" t="inlineStr">
-        <is>
-          <t>[14 Oct 2026] Aditya Infotech (NSEI:CPPLUS) Stock Forecast &amp; Analyst Predictions - Simply Wall Street | [14 Oct 2026] CPPLUS Share Price Near 52-Week High: Key Stock Analysis - Univest | [14 Oct 2026] Aditya Infotech (NSE:CPPLUS): What Does the Q2 FY27 Share Capital Audit Show? - Kalkine India | [15 Oct 2026] Dynamic Services &amp; Security Share Price today at Rs 130 - Univest</t>
-        </is>
-      </c>
+          <t>RELAXED smallcap</t>
+        </is>
+      </c>
+      <c r="AK23" s="7" t="inlineStr"/>
       <c r="AL23" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -6512,22 +6528,18 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>RUBYMILLS</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Just Dial Limited</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Consumer Services</t>
-        </is>
-      </c>
+          <t>The Ruby Mills Limited</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -6536,7 +6548,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -6544,80 +6556,88 @@
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>713.25</v>
+        <v>517.7000122070312</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>713.25</v>
+        <v>515.95</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>706.1174999999999</v>
+        <v>512.5230120849609</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>720.3825000000001</v>
+        <v>522.8770123291016</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>673.1319549905328</v>
+        <v>484.0495114135742</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>5.624682090356426</v>
+        <v>6.499999999999996</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>763.1775</v>
+        <v>553.9390130615235</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>784.575</v>
+        <v>569.4700134277344</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>1.244514781022304</v>
+        <v>1.076923076923079</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>1.777878258603292</v>
+        <v>1.538461538461541</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>17118</v>
-      </c>
-      <c r="U24" s="6" t="inlineStr"/>
-      <c r="V24" s="6" t="inlineStr"/>
+        <v>15013.30035400391</v>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v>75.75757575757575</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>75.75757575757575</v>
+      </c>
       <c r="W24" s="5" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>4.913118796071611</v>
+        <v>5.210256081756946</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>64.37933294993516</v>
+        <v>60.67278996549893</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>14.89965877420833</v>
+        <v>33.58862248503914</v>
       </c>
       <c r="AA24" s="8" t="n">
-        <v>3.124823383531349</v>
+        <v>7.062004229321539</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>5.870563615310553</v>
+        <v>20.37836742351884</v>
       </c>
       <c r="AC24" s="8" t="n">
-        <v>-7.044179415203167</v>
+        <v>29.82067919258611</v>
       </c>
       <c r="AD24" s="8" t="n">
-        <v>6.178300935068403</v>
+        <v>20.68610474327669</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>-18.81971092426513</v>
-      </c>
-      <c r="AF24" s="6" t="inlineStr"/>
+        <v>-11.31477306945932</v>
+      </c>
+      <c r="AF24" s="6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AG24" s="6" t="inlineStr"/>
       <c r="AH24" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI24" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 4.9x avg | OBV rising | Closed above prior 20D high | Beating NIFTY 1M</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | ADX&gt;=25 strong trend | Volume 5.2x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 76% of similar setups</t>
         </is>
       </c>
       <c r="AJ24" s="7" t="inlineStr">
@@ -6625,7 +6645,11 @@
           <t>RELAXED smallcap</t>
         </is>
       </c>
-      <c r="AK24" s="7" t="inlineStr"/>
+      <c r="AK24" s="7" t="inlineStr">
+        <is>
+          <t>[13 Oct 2026] Ruby Mills (NSE:RUBYMILLS): Did It File the Required Depository Compliance Certificate for Q2 FY27? - Kalkine India | [12 Oct 2026] Binayak Tex Processors Limited (ZBINTXPP.BO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+        </is>
+      </c>
       <c r="AL24" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -6745,7 +6769,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: NEUTRAL | Generated: 17-Oct-2026 13:29 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: NEUTRAL | Generated: 17-Oct-2026 13:50 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6995,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>211.9499969482422</v>
@@ -6980,10 +7004,10 @@
         <v>192.981180653223</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>184.378315091377</v>
+        <v>184.3783150913705</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>147.5462228265307</v>
+        <v>147.5462228185293</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>71.27322343616365</v>
@@ -6998,13 +7022,13 @@
         <v>2.242387067539511</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>20.75038304203383</v>
+        <v>20.75038304203368</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>32.4279949625122</v>
+        <v>32.42799496251222</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>14.0561072997443</v>
+        <v>14.05610729974431</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>7.915613325694602</v>
@@ -7024,10 +7048,10 @@
         <v>3.338723363253818</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>1.168702371495603</v>
+        <v>1.168702371495604</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>17.03465390898321</v>
+        <v>17.03465390898318</v>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
@@ -7072,12 +7096,22 @@
       <c r="AI5" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ5" s="6" t="inlineStr"/>
-      <c r="AK5" s="6" t="inlineStr"/>
+      <c r="AJ5" s="5" t="n">
+        <v>6452.0192</v>
+      </c>
+      <c r="AK5" s="8" t="n">
+        <v>39.98276</v>
+      </c>
       <c r="AL5" s="6" t="inlineStr"/>
-      <c r="AM5" s="6" t="inlineStr"/>
-      <c r="AN5" s="6" t="inlineStr"/>
-      <c r="AO5" s="6" t="inlineStr"/>
+      <c r="AM5" s="8" t="n">
+        <v>1.30807</v>
+      </c>
+      <c r="AN5" s="8" t="n">
+        <v>34.59999999999999</v>
+      </c>
+      <c r="AO5" s="8" t="n">
+        <v>53.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -7094,7 +7128,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>249.3899993896484</v>
@@ -7195,12 +7229,22 @@
       <c r="AI6" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ6" s="6" t="inlineStr"/>
-      <c r="AK6" s="6" t="inlineStr"/>
+      <c r="AJ6" s="5" t="n">
+        <v>450.1174272</v>
+      </c>
+      <c r="AK6" s="8" t="n">
+        <v>22.346775</v>
+      </c>
       <c r="AL6" s="6" t="inlineStr"/>
-      <c r="AM6" s="6" t="inlineStr"/>
-      <c r="AN6" s="6" t="inlineStr"/>
-      <c r="AO6" s="6" t="inlineStr"/>
+      <c r="AM6" s="8" t="n">
+        <v>2.03436</v>
+      </c>
+      <c r="AN6" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AO6" s="8" t="n">
+        <v>11.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -7217,7 +7261,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>232.1499938964844</v>
@@ -7316,12 +7360,22 @@
       <c r="AI7" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ7" s="6" t="inlineStr"/>
-      <c r="AK7" s="6" t="inlineStr"/>
+      <c r="AJ7" s="5" t="n">
+        <v>2431.1832576</v>
+      </c>
+      <c r="AK7" s="8" t="n">
+        <v>19.829391</v>
+      </c>
       <c r="AL7" s="6" t="inlineStr"/>
-      <c r="AM7" s="6" t="inlineStr"/>
-      <c r="AN7" s="6" t="inlineStr"/>
-      <c r="AO7" s="6" t="inlineStr"/>
+      <c r="AM7" s="8" t="n">
+        <v>0.8203199999999999</v>
+      </c>
+      <c r="AN7" s="8" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AO7" s="8" t="n">
+        <v>81.10000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -7338,7 +7392,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>772.0999755859375</v>
@@ -7439,12 +7493,22 @@
       <c r="AI8" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ8" s="6" t="inlineStr"/>
-      <c r="AK8" s="6" t="inlineStr"/>
+      <c r="AJ8" s="5" t="n">
+        <v>111692.4280832</v>
+      </c>
+      <c r="AK8" s="8" t="n">
+        <v>51.23424</v>
+      </c>
       <c r="AL8" s="6" t="inlineStr"/>
-      <c r="AM8" s="6" t="inlineStr"/>
-      <c r="AN8" s="6" t="inlineStr"/>
-      <c r="AO8" s="6" t="inlineStr"/>
+      <c r="AM8" s="8" t="n">
+        <v>0.18987</v>
+      </c>
+      <c r="AN8" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AO8" s="8" t="n">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -7461,7 +7525,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>345.6499938964844</v>
@@ -7562,12 +7626,22 @@
       <c r="AI9" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="6" t="inlineStr"/>
-      <c r="AL9" s="6" t="inlineStr"/>
+      <c r="AJ9" s="5" t="n">
+        <v>34379.5204096</v>
+      </c>
+      <c r="AK9" s="8" t="n">
+        <v>11.962664</v>
+      </c>
+      <c r="AL9" s="8" t="n">
+        <v>20.989001</v>
+      </c>
       <c r="AM9" s="6" t="inlineStr"/>
-      <c r="AN9" s="6" t="inlineStr"/>
-      <c r="AO9" s="6" t="inlineStr"/>
+      <c r="AN9" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO9" s="8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -7584,7 +7658,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>151.8000030517578</v>
@@ -7685,12 +7759,24 @@
       <c r="AI10" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="6" t="inlineStr"/>
-      <c r="AL10" s="6" t="inlineStr"/>
-      <c r="AM10" s="6" t="inlineStr"/>
-      <c r="AN10" s="6" t="inlineStr"/>
-      <c r="AO10" s="6" t="inlineStr"/>
+      <c r="AJ10" s="5" t="n">
+        <v>2711.1356416</v>
+      </c>
+      <c r="AK10" s="8" t="n">
+        <v>40.37234</v>
+      </c>
+      <c r="AL10" s="8" t="n">
+        <v>9.110999999999999</v>
+      </c>
+      <c r="AM10" s="8" t="n">
+        <v>0.14488</v>
+      </c>
+      <c r="AN10" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO10" s="8" t="n">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -7707,46 +7793,46 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>1198.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1095.203946595185</v>
+        <v>1095.203946613352</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>1063.443916992846</v>
+        <v>1063.443917548658</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>967.3193646145411</v>
+        <v>967.3193659144735</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>74.30427637137547</v>
+        <v>74.30427558647924</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>22.75136637610967</v>
+        <v>22.75136630597149</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>11.03693212897725</v>
+        <v>11.03693202659918</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>11.71443424713242</v>
+        <v>11.71443427937231</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>20.13124034134543</v>
+        <v>20.13123882223714</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>35.7503008839136</v>
+        <v>35.7503007465514</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>10.66854829567617</v>
+        <v>10.66854840425631</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>36.99230029717901</v>
+        <v>36.99230046509869</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>3.08654987878006</v>
+        <v>3.08654989279088</v>
       </c>
       <c r="R11" s="8" t="n">
         <v>1.586297030055078</v>
@@ -7760,10 +7846,10 @@
         <v>3.259818641580505</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>1.178400466641015</v>
+        <v>1.178400466641124</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>14.76220487444599</v>
+        <v>14.76220487444362</v>
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
@@ -7795,7 +7881,7 @@
         <v>-2.003270645952571</v>
       </c>
       <c r="AF11" s="8" t="n">
-        <v>9.43167286110922</v>
+        <v>9.431672859294004</v>
       </c>
       <c r="AG11" s="6" t="inlineStr">
         <is>
@@ -7808,12 +7894,22 @@
       <c r="AI11" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="6" t="inlineStr"/>
+      <c r="AJ11" s="5" t="n">
+        <v>33364.1252864</v>
+      </c>
+      <c r="AK11" s="8" t="n">
+        <v>29.902693</v>
+      </c>
       <c r="AL11" s="6" t="inlineStr"/>
-      <c r="AM11" s="6" t="inlineStr"/>
-      <c r="AN11" s="6" t="inlineStr"/>
-      <c r="AO11" s="6" t="inlineStr"/>
+      <c r="AM11" s="8" t="n">
+        <v>0.08132999999999999</v>
+      </c>
+      <c r="AN11" s="8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AO11" s="8" t="n">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -7830,7 +7926,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>100.620002746582</v>
@@ -7931,12 +8027,22 @@
       <c r="AI12" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="6" t="inlineStr"/>
+      <c r="AJ12" s="5" t="n">
+        <v>9770.184703999999</v>
+      </c>
+      <c r="AK12" s="8" t="n">
+        <v>14.191819</v>
+      </c>
       <c r="AL12" s="6" t="inlineStr"/>
-      <c r="AM12" s="6" t="inlineStr"/>
-      <c r="AN12" s="6" t="inlineStr"/>
-      <c r="AO12" s="6" t="inlineStr"/>
+      <c r="AM12" s="8" t="n">
+        <v>0.74729</v>
+      </c>
+      <c r="AN12" s="8" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AO12" s="8" t="n">
+        <v>108.3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -7953,7 +8059,7 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>239.1000061035156</v>
@@ -8054,11 +8160,19 @@
       <c r="AI13" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="6" t="inlineStr"/>
+      <c r="AJ13" s="5" t="n">
+        <v>2243.7257216</v>
+      </c>
+      <c r="AK13" s="8" t="n">
+        <v>62.8027</v>
+      </c>
       <c r="AL13" s="6" t="inlineStr"/>
-      <c r="AM13" s="6" t="inlineStr"/>
-      <c r="AN13" s="6" t="inlineStr"/>
+      <c r="AM13" s="8" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="AN13" s="8" t="n">
+        <v>63.5</v>
+      </c>
       <c r="AO13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
@@ -8076,7 +8190,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>159.0700073242188</v>
@@ -8178,11 +8292,19 @@
         <v>-4.882615700799143</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="6" t="inlineStr"/>
+      <c r="AK14" s="8" t="n">
+        <v>26.203478</v>
+      </c>
       <c r="AL14" s="6" t="inlineStr"/>
-      <c r="AM14" s="6" t="inlineStr"/>
-      <c r="AN14" s="6" t="inlineStr"/>
-      <c r="AO14" s="6" t="inlineStr"/>
+      <c r="AM14" s="8" t="n">
+        <v>0.4944</v>
+      </c>
+      <c r="AN14" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AO14" s="8" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -8199,7 +8321,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>571.9000244140625</v>
@@ -8208,10 +8330,10 @@
         <v>548.8768097297327</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>544.4013005430722</v>
+        <v>544.4013005430726</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>526.5719327916684</v>
+        <v>526.5719327939339</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>60.11523314088968</v>
@@ -8252,10 +8374,10 @@
         <v>2.42308192739732</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>1.160573054313498</v>
+        <v>1.160573054314721</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>5.680149775331894</v>
+        <v>5.680149775321375</v>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
@@ -8300,12 +8422,22 @@
       <c r="AI15" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="6" t="inlineStr"/>
+      <c r="AJ15" s="5" t="n">
+        <v>48567.205888</v>
+      </c>
+      <c r="AK15" s="8" t="n">
+        <v>23.097738</v>
+      </c>
       <c r="AL15" s="6" t="inlineStr"/>
-      <c r="AM15" s="6" t="inlineStr"/>
-      <c r="AN15" s="6" t="inlineStr"/>
-      <c r="AO15" s="6" t="inlineStr"/>
+      <c r="AM15" s="8" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="AN15" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AO15" s="8" t="n">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -8322,7 +8454,7 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>798.2000122070312</v>
@@ -8423,12 +8555,22 @@
       <c r="AI16" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="6" t="inlineStr"/>
+      <c r="AJ16" s="5" t="n">
+        <v>10063.2584192</v>
+      </c>
+      <c r="AK16" s="8" t="n">
+        <v>80.953354</v>
+      </c>
       <c r="AL16" s="6" t="inlineStr"/>
-      <c r="AM16" s="6" t="inlineStr"/>
-      <c r="AN16" s="6" t="inlineStr"/>
-      <c r="AO16" s="6" t="inlineStr"/>
+      <c r="AM16" s="8" t="n">
+        <v>0.16781</v>
+      </c>
+      <c r="AN16" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AO16" s="8" t="n">
+        <v>34.59999999999999</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -8445,7 +8587,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>51.45000076293945</v>
@@ -8454,10 +8596,10 @@
         <v>48.47549007757899</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>47.18626846726397</v>
+        <v>47.18626846726302</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>42.7373294560501</v>
+        <v>42.73732945394237</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>66.88693298468556</v>
@@ -8472,7 +8614,7 @@
         <v>0.335159839076705</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>21.60310896302366</v>
+        <v>21.60310896302359</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>29.4625074847687</v>
@@ -8498,10 +8640,10 @@
         <v>2.444600656201386</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>0.9553484451863131</v>
+        <v>0.9553484451860653</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>14.55766640183848</v>
+        <v>14.55766640184641</v>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
@@ -8512,7 +8654,7 @@
         <v>83.56808548743359</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>83.58688826567492</v>
+        <v>83.5868882656749</v>
       </c>
       <c r="Z17" s="8" t="n">
         <v>-0.0582726875750339</v>
@@ -8546,12 +8688,22 @@
       <c r="AI17" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="6" t="inlineStr"/>
-      <c r="AL17" s="6" t="inlineStr"/>
+      <c r="AJ17" s="5" t="n">
+        <v>13477.3465088</v>
+      </c>
+      <c r="AK17" s="8" t="n">
+        <v>8.518212</v>
+      </c>
+      <c r="AL17" s="8" t="n">
+        <v>13.949999</v>
+      </c>
       <c r="AM17" s="6" t="inlineStr"/>
-      <c r="AN17" s="6" t="inlineStr"/>
-      <c r="AO17" s="6" t="inlineStr"/>
+      <c r="AN17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO17" s="8" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -8568,7 +8720,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>301.5499877929688</v>
@@ -8669,12 +8821,22 @@
       <c r="AI18" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="6" t="inlineStr"/>
+      <c r="AJ18" s="5" t="n">
+        <v>19227.4644992</v>
+      </c>
+      <c r="AK18" s="8" t="n">
+        <v>35.10477</v>
+      </c>
       <c r="AL18" s="6" t="inlineStr"/>
-      <c r="AM18" s="6" t="inlineStr"/>
-      <c r="AN18" s="6" t="inlineStr"/>
-      <c r="AO18" s="6" t="inlineStr"/>
+      <c r="AM18" s="8" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="AN18" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO18" s="8" t="n">
+        <v>-75.40000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -8691,46 +8853,46 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>4989</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>4804.014310368752</v>
+        <v>4804.014310368757</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>4768.71626266451</v>
+        <v>4768.716262746453</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>4550.478979577971</v>
+        <v>4550.478981426691</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>60.50147794142603</v>
+        <v>60.50147794130429</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>23.85691559793941</v>
+        <v>23.85691559780571</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>-9.29599439398063</v>
+        <v>-9.295994394178077</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>33.15290999192003</v>
+        <v>33.15290999198379</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>15.79813209030593</v>
+        <v>15.79813208845606</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>28.29662003263611</v>
+        <v>28.29662003264327</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>22.72279772086016</v>
+        <v>22.72279772097486</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>110.841817872415</v>
+        <v>110.841817872794</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>2.221724150579576</v>
+        <v>2.221724150587171</v>
       </c>
       <c r="R19" s="8" t="n">
         <v>1.397115867530088</v>
@@ -8744,10 +8906,10 @@
         <v>2.559128915410556</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>0.9853726289455312</v>
+        <v>0.9853726289456858</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>9.46114766605703</v>
+        <v>9.461147666054018</v>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
@@ -8758,7 +8920,7 @@
         <v>100</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>95.28748056802804</v>
+        <v>95.28748056802806</v>
       </c>
       <c r="Z19" s="8" t="n">
         <v>1.608961303462331</v>
@@ -8779,7 +8941,7 @@
         <v>-3.124330674282105</v>
       </c>
       <c r="AF19" s="8" t="n">
-        <v>3.850648180459904</v>
+        <v>3.850648180459793</v>
       </c>
       <c r="AG19" s="6" t="inlineStr">
         <is>
@@ -8792,12 +8954,22 @@
       <c r="AI19" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="6" t="inlineStr"/>
+      <c r="AJ19" s="5" t="n">
+        <v>333651.8238208</v>
+      </c>
+      <c r="AK19" s="8" t="n">
+        <v>35.79423</v>
+      </c>
       <c r="AL19" s="6" t="inlineStr"/>
-      <c r="AM19" s="6" t="inlineStr"/>
-      <c r="AN19" s="6" t="inlineStr"/>
-      <c r="AO19" s="6" t="inlineStr"/>
+      <c r="AM19" s="8" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AN19" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AO19" s="8" t="n">
+        <v>14.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -8814,7 +8986,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>219.4199981689453</v>
@@ -8915,12 +9087,22 @@
       <c r="AI20" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="6" t="inlineStr"/>
+      <c r="AJ20" s="5" t="n">
+        <v>1486.3934464</v>
+      </c>
+      <c r="AK20" s="8" t="n">
+        <v>17.03483</v>
+      </c>
       <c r="AL20" s="6" t="inlineStr"/>
-      <c r="AM20" s="6" t="inlineStr"/>
-      <c r="AN20" s="6" t="inlineStr"/>
-      <c r="AO20" s="6" t="inlineStr"/>
+      <c r="AM20" s="8" t="n">
+        <v>0.04253</v>
+      </c>
+      <c r="AN20" s="8" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AO20" s="8" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -8937,7 +9119,7 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E21" s="9" t="n">
         <v>577.2000122070312</v>
@@ -8946,37 +9128,37 @@
         <v>528.1469186249088</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>506.7473775349762</v>
+        <v>506.7473775359442</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>450.5559554423958</v>
+        <v>450.5559558917843</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>65.74727172695339</v>
+        <v>65.74727172697395</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>18.05378684975915</v>
+        <v>18.05378684976313</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>10.74413507374406</v>
+        <v>10.74413507374982</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>7.309651776015091</v>
+        <v>7.309651776013304</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>26.59906531119446</v>
+        <v>26.59906531042339</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>33.57515238724748</v>
+        <v>33.57515238725176</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>9.407624313831123</v>
+        <v>9.407624313860131</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>29.79796036094523</v>
+        <v>29.79796036095424</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>5.162501685855343</v>
+        <v>5.162501685856903</v>
       </c>
       <c r="R21" s="8" t="n">
         <v>1.59901391623494</v>
@@ -8990,10 +9172,10 @@
         <v>4.810769395982025</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>0.9200355923000579</v>
+        <v>0.920035592300093</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>23.29391417561595</v>
+        <v>23.29391417561401</v>
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
@@ -9004,7 +9186,7 @@
         <v>72.88379523098239</v>
       </c>
       <c r="Y21" s="8" t="n">
-        <v>77.09212737199105</v>
+        <v>77.09212737199107</v>
       </c>
       <c r="Z21" s="8" t="n">
         <v>-3.219317810373068</v>
@@ -9038,12 +9220,22 @@
       <c r="AI21" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="6" t="inlineStr"/>
+      <c r="AJ21" s="5" t="n">
+        <v>5913.6290816</v>
+      </c>
+      <c r="AK21" s="8" t="n">
+        <v>32.178513</v>
+      </c>
       <c r="AL21" s="6" t="inlineStr"/>
-      <c r="AM21" s="6" t="inlineStr"/>
-      <c r="AN21" s="6" t="inlineStr"/>
-      <c r="AO21" s="6" t="inlineStr"/>
+      <c r="AM21" s="8" t="n">
+        <v>0.73233</v>
+      </c>
+      <c r="AN21" s="8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AO21" s="8" t="n">
+        <v>51.6</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -9060,7 +9252,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>1030.099975585938</v>
@@ -9161,12 +9353,24 @@
       <c r="AI22" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="6" t="inlineStr"/>
-      <c r="AL22" s="6" t="inlineStr"/>
-      <c r="AM22" s="6" t="inlineStr"/>
-      <c r="AN22" s="6" t="inlineStr"/>
-      <c r="AO22" s="6" t="inlineStr"/>
+      <c r="AJ22" s="5" t="n">
+        <v>7122.6728448</v>
+      </c>
+      <c r="AK22" s="8" t="n">
+        <v>73.9695</v>
+      </c>
+      <c r="AL22" s="8" t="n">
+        <v>8.175000499999999</v>
+      </c>
+      <c r="AM22" s="8" t="n">
+        <v>0.19061</v>
+      </c>
+      <c r="AN22" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AO22" s="8" t="n">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -9183,7 +9387,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>546.7000122070312</v>
@@ -9284,12 +9488,22 @@
       <c r="AI23" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="6" t="inlineStr"/>
+      <c r="AJ23" s="5" t="n">
+        <v>4698.3520256</v>
+      </c>
+      <c r="AK23" s="8" t="n">
+        <v>78.84560999999999</v>
+      </c>
       <c r="AL23" s="6" t="inlineStr"/>
-      <c r="AM23" s="6" t="inlineStr"/>
-      <c r="AN23" s="6" t="inlineStr"/>
-      <c r="AO23" s="6" t="inlineStr"/>
+      <c r="AM23" s="8" t="n">
+        <v>0.8077</v>
+      </c>
+      <c r="AN23" s="8" t="n">
+        <v>79.10000000000001</v>
+      </c>
+      <c r="AO23" s="8" t="n">
+        <v>-41.09999999999999</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -9306,7 +9520,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>399.5</v>
@@ -9407,12 +9621,22 @@
       <c r="AI24" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="6" t="inlineStr"/>
+      <c r="AJ24" s="5" t="n">
+        <v>3040.8882176</v>
+      </c>
+      <c r="AK24" s="8" t="n">
+        <v>63.513515</v>
+      </c>
       <c r="AL24" s="6" t="inlineStr"/>
-      <c r="AM24" s="6" t="inlineStr"/>
-      <c r="AN24" s="6" t="inlineStr"/>
-      <c r="AO24" s="6" t="inlineStr"/>
+      <c r="AM24" s="8" t="n">
+        <v>2.21076</v>
+      </c>
+      <c r="AN24" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="AO24" s="8" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -9429,46 +9653,46 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E25" s="9" t="n">
         <v>1380</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1261.802878134973</v>
+        <v>1261.802878106188</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>1255.290452310035</v>
+        <v>1255.29045163931</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>1297.413279588849</v>
+        <v>1297.413278895164</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>70.16445404447384</v>
+        <v>70.16445417213112</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>15.93767893044514</v>
+        <v>15.93767903943012</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>-4.693682633992755</v>
+        <v>-4.693682474703019</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>20.6313615644379</v>
+        <v>20.63136151413314</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>21.39035122212736</v>
+        <v>21.39035001172544</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>35.16628217908194</v>
+        <v>35.16628232110492</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>13.33118855006218</v>
+        <v>13.33118883004452</v>
       </c>
       <c r="P25" s="9" t="n">
-        <v>39.4816497099562</v>
+        <v>39.48164973634176</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>2.860989109417116</v>
+        <v>2.860989111329113</v>
       </c>
       <c r="R25" s="8" t="n">
         <v>1.546948642665332</v>
@@ -9482,10 +9706,10 @@
         <v>6.500384397142769</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>1.096965247073503</v>
+        <v>1.09696524707362</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>18.1772936718784</v>
+        <v>18.17729367187482</v>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
@@ -9496,7 +9720,7 @@
         <v>97.84120150687784</v>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>91.75100154832965</v>
+        <v>91.75100154832967</v>
       </c>
       <c r="Z25" s="8" t="n">
         <v>2.373887240356076</v>
@@ -9514,10 +9738,10 @@
         <v>1.190845393127882</v>
       </c>
       <c r="AE25" s="8" t="n">
-        <v>-19.47495052488568</v>
+        <v>-19.47495654757913</v>
       </c>
       <c r="AF25" s="8" t="n">
-        <v>9.36732067371171</v>
+        <v>9.367320676206647</v>
       </c>
       <c r="AG25" s="6" t="inlineStr">
         <is>
@@ -9530,12 +9754,24 @@
       <c r="AI25" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="6" t="inlineStr"/>
-      <c r="AL25" s="6" t="inlineStr"/>
-      <c r="AM25" s="6" t="inlineStr"/>
-      <c r="AN25" s="6" t="inlineStr"/>
-      <c r="AO25" s="6" t="inlineStr"/>
+      <c r="AJ25" s="5" t="n">
+        <v>373395.7902336</v>
+      </c>
+      <c r="AK25" s="8" t="n">
+        <v>20.417223</v>
+      </c>
+      <c r="AL25" s="8" t="n">
+        <v>24.648</v>
+      </c>
+      <c r="AM25" s="8" t="n">
+        <v>0.07905000000000001</v>
+      </c>
+      <c r="AN25" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO25" s="8" t="n">
+        <v>10.8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -9552,7 +9788,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>1998.199951171875</v>
@@ -9653,12 +9889,22 @@
       <c r="AI26" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="6" t="inlineStr"/>
+      <c r="AJ26" s="5" t="n">
+        <v>18009.3452288</v>
+      </c>
+      <c r="AK26" s="8" t="n">
+        <v>25.022375</v>
+      </c>
       <c r="AL26" s="6" t="inlineStr"/>
-      <c r="AM26" s="6" t="inlineStr"/>
-      <c r="AN26" s="6" t="inlineStr"/>
-      <c r="AO26" s="6" t="inlineStr"/>
+      <c r="AM26" s="8" t="n">
+        <v>0.15012</v>
+      </c>
+      <c r="AN26" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AO26" s="8" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -9666,7 +9912,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -9675,49 +9921,49 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>418.1499938964844</v>
+        <v>596.5</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>388.1240445965179</v>
+        <v>573.2055180642128</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>368.4000815984194</v>
+        <v>547.5881600611494</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>316.8521185238406</v>
+        <v>484.8193371035669</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>73.72559863121177</v>
+        <v>62.29406094460268</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>11.5120867822892</v>
+        <v>15.8832737597271</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>8.846733525004369</v>
+        <v>13.30289343366742</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>2.665353257284833</v>
+        <v>2.580380326059684</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>35.3737148672471</v>
+        <v>38.67790500869441</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>32.37638876269169</v>
+        <v>26.19797393741519</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>7.929848847742432</v>
+        <v>5.751059604792266</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>13.68694448231809</v>
+        <v>27.26684787305209</v>
       </c>
       <c r="Q27" s="8" t="n">
-        <v>3.273214081573411</v>
+        <v>4.571139626664222</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>0.9869207715361562</v>
+        <v>8.266304109774618</v>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
@@ -9725,13 +9971,13 @@
         </is>
       </c>
       <c r="T27" s="8" t="n">
-        <v>2.036197795020728</v>
+        <v>2.589228200345134</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>1.062296503965187</v>
+        <v>0.7914292558882393</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>15.08739269437165</v>
+        <v>18.66315711246307</v>
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
@@ -9739,31 +9985,31 @@
         </is>
       </c>
       <c r="X27" s="8" t="n">
-        <v>96.41025641025641</v>
+        <v>57.97269051535088</v>
       </c>
       <c r="Y27" s="8" t="n">
-        <v>92.12511177586968</v>
+        <v>74.37509826464068</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>2.81533841794539</v>
+        <v>0.879420313611079</v>
       </c>
       <c r="AA27" s="8" t="n">
-        <v>10.72421571681561</v>
+        <v>1.627053001849199</v>
       </c>
       <c r="AB27" s="8" t="n">
-        <v>19.08016550322109</v>
+        <v>14.17360246201409</v>
       </c>
       <c r="AC27" s="8" t="n">
-        <v>37.25586813521016</v>
+        <v>22.92632663575476</v>
       </c>
       <c r="AD27" s="8" t="n">
-        <v>1.92565360060557</v>
+        <v>-3.086921202274573</v>
       </c>
       <c r="AE27" s="8" t="n">
-        <v>-0.4167659027000226</v>
+        <v>-8.287211314701349</v>
       </c>
       <c r="AF27" s="8" t="n">
-        <v>7.736173452273643</v>
+        <v>4.063897014539486</v>
       </c>
       <c r="AG27" s="6" t="inlineStr">
         <is>
@@ -9776,12 +10022,24 @@
       <c r="AI27" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="6" t="inlineStr"/>
-      <c r="AL27" s="6" t="inlineStr"/>
-      <c r="AM27" s="6" t="inlineStr"/>
-      <c r="AN27" s="6" t="inlineStr"/>
-      <c r="AO27" s="6" t="inlineStr"/>
+      <c r="AJ27" s="5" t="n">
+        <v>20581.8249216</v>
+      </c>
+      <c r="AK27" s="8" t="n">
+        <v>34.219875</v>
+      </c>
+      <c r="AL27" s="8" t="n">
+        <v>7.237</v>
+      </c>
+      <c r="AM27" s="8" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="AN27" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AO27" s="8" t="n">
+        <v>20.4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -9789,7 +10047,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>WSTCSTPAPR</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -9798,49 +10056,49 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>596.5</v>
+        <v>822.4000244140625</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>573.2055180642128</v>
+        <v>765.6691868757766</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>547.5881600611494</v>
+        <v>697.5723917175146</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>484.8193371035669</v>
+        <v>566.1065814297787</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>62.29406094460268</v>
+        <v>57.54259144072577</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>15.8832737597271</v>
+        <v>44.75378751122139</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>13.30289343366742</v>
+        <v>33.74007095988557</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>2.580380326059684</v>
+        <v>11.01371655133582</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>38.67790500869441</v>
+        <v>43.40740447414429</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>26.19797393741519</v>
+        <v>37.5271531379606</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>5.751059604792266</v>
+        <v>7.651605947522599</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>27.26684787305209</v>
+        <v>54.85078431037627</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>4.571139626664222</v>
+        <v>6.669599061534069</v>
       </c>
       <c r="R28" s="8" t="n">
-        <v>8.266304109774618</v>
+        <v>1.70697963357593</v>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
@@ -9848,45 +10106,45 @@
         </is>
       </c>
       <c r="T28" s="8" t="n">
-        <v>2.589228200345134</v>
+        <v>2.920932025944726</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>0.7914292558882393</v>
+        <v>0.7559322462129708</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>18.66315711246307</v>
+        <v>31.80427743851582</v>
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X28" s="8" t="n">
-        <v>57.97269051535088</v>
+        <v>45.20331981413339</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>74.37509826464068</v>
+        <v>68.95850406340263</v>
       </c>
       <c r="Z28" s="8" t="n">
-        <v>0.879420313611079</v>
+        <v>-12.55250000113575</v>
       </c>
       <c r="AA28" s="8" t="n">
-        <v>1.627053001849199</v>
+        <v>15.32745092836607</v>
       </c>
       <c r="AB28" s="8" t="n">
-        <v>14.17360246201409</v>
+        <v>15.29511264379264</v>
       </c>
       <c r="AC28" s="8" t="n">
-        <v>22.92632663575476</v>
+        <v>57.06202598117125</v>
       </c>
       <c r="AD28" s="8" t="n">
-        <v>-3.086921202274573</v>
+        <v>-15.9143157631585</v>
       </c>
       <c r="AE28" s="8" t="n">
-        <v>-8.287211314701349</v>
+        <v>-15.9143157631585</v>
       </c>
       <c r="AF28" s="8" t="n">
-        <v>4.063897014539486</v>
+        <v>7.409314428567959</v>
       </c>
       <c r="AG28" s="6" t="inlineStr">
         <is>
@@ -9899,12 +10157,22 @@
       <c r="AI28" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="6" t="inlineStr"/>
+      <c r="AJ28" s="5" t="n">
+        <v>5548.1081856</v>
+      </c>
+      <c r="AK28" s="8" t="n">
+        <v>24.669603</v>
+      </c>
       <c r="AL28" s="6" t="inlineStr"/>
-      <c r="AM28" s="6" t="inlineStr"/>
-      <c r="AN28" s="6" t="inlineStr"/>
-      <c r="AO28" s="6" t="inlineStr"/>
+      <c r="AM28" s="8" t="n">
+        <v>0.08243</v>
+      </c>
+      <c r="AN28" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AO28" s="8" t="n">
+        <v>145.3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -9912,58 +10180,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>TEXINFRA</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>123.9800033569336</v>
+        <v>418.1499938964844</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>119.1175222236475</v>
+        <v>388.1240445965179</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>115.9315833634613</v>
+        <v>368.4000815984194</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>107.59327087597</v>
+        <v>316.8521185238406</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>59.47946329370782</v>
+        <v>73.72559863121177</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1.870559550670066</v>
+        <v>11.5120867822892</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1.693048044028185</v>
+        <v>8.846733525004369</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.1775115066418813</v>
+        <v>2.665353257284833</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>26.3544226690262</v>
+        <v>35.3737148672471</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>31.44210907696054</v>
+        <v>32.37638876269169</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>15.27102892926532</v>
+        <v>7.929848847742432</v>
       </c>
       <c r="P29" s="9" t="n">
-        <v>5.309555278858124</v>
+        <v>13.68694448231809</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>4.282590042824988</v>
+        <v>3.273214081573411</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>1.393805643299728</v>
+        <v>0.9869207715361562</v>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
@@ -9971,13 +10239,13 @@
         </is>
       </c>
       <c r="T29" s="8" t="n">
-        <v>1.108801033720714</v>
+        <v>2.036197795020728</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>0.8643724421085509</v>
+        <v>1.062296503965187</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>11.78702891561928</v>
+        <v>15.08739269437165</v>
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
@@ -9985,31 +10253,31 @@
         </is>
       </c>
       <c r="X29" s="8" t="n">
-        <v>71.4368084214514</v>
+        <v>96.41025641025641</v>
       </c>
       <c r="Y29" s="8" t="n">
-        <v>68.60191048233935</v>
+        <v>92.12511177586968</v>
       </c>
       <c r="Z29" s="8" t="n">
-        <v>0.9033943074298723</v>
+        <v>2.81533841794539</v>
       </c>
       <c r="AA29" s="8" t="n">
-        <v>3.28224126237624</v>
+        <v>10.72421571681561</v>
       </c>
       <c r="AB29" s="8" t="n">
-        <v>8.687651169125953</v>
+        <v>19.08016550322109</v>
       </c>
       <c r="AC29" s="8" t="n">
-        <v>8.91550755946473</v>
+        <v>37.25586813521016</v>
       </c>
       <c r="AD29" s="8" t="n">
-        <v>-2.377950112650717</v>
+        <v>1.92565360060557</v>
       </c>
       <c r="AE29" s="8" t="n">
-        <v>-3.854202178309041</v>
+        <v>-0.4167659027000226</v>
       </c>
       <c r="AF29" s="8" t="n">
-        <v>4.082087204732665</v>
+        <v>7.736173452273643</v>
       </c>
       <c r="AG29" s="6" t="inlineStr">
         <is>
@@ -10022,11 +10290,17 @@
       <c r="AI29" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ29" s="6" t="inlineStr"/>
+      <c r="AJ29" s="5" t="n">
+        <v>17084.678144</v>
+      </c>
       <c r="AK29" s="6" t="inlineStr"/>
       <c r="AL29" s="6" t="inlineStr"/>
-      <c r="AM29" s="6" t="inlineStr"/>
-      <c r="AN29" s="6" t="inlineStr"/>
+      <c r="AM29" s="8" t="n">
+        <v>0.06051</v>
+      </c>
+      <c r="AN29" s="8" t="n">
+        <v>-14</v>
+      </c>
       <c r="AO29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
@@ -10035,58 +10309,58 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>WSTCSTPAPR</t>
+          <t>AVTNPL</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>822.4000244140625</v>
+        <v>99.75</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>765.6691868757766</v>
+        <v>92.52507767985948</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>697.5723917175146</v>
+        <v>87.35881901374442</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>566.1065814297787</v>
+        <v>75.6981598196834</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>57.54259144072577</v>
+        <v>63.0830508635324</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>44.75378751122139</v>
+        <v>2.734269495025188</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>33.74007095988557</v>
+        <v>2.01094510136765</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>11.01371655133582</v>
+        <v>0.723324393657538</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>43.40740447414429</v>
+        <v>25.834372514938</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>37.5271531379606</v>
+        <v>30.14710669262486</v>
       </c>
       <c r="O30" s="8" t="n">
-        <v>7.651605947522599</v>
+        <v>15.55463748710341</v>
       </c>
       <c r="P30" s="9" t="n">
-        <v>54.85078431037627</v>
+        <v>5.828997856599047</v>
       </c>
       <c r="Q30" s="8" t="n">
-        <v>6.669599061534069</v>
+        <v>5.843606873783505</v>
       </c>
       <c r="R30" s="8" t="n">
-        <v>1.70697963357593</v>
+        <v>1.48474111643167</v>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
@@ -10094,45 +10368,45 @@
         </is>
       </c>
       <c r="T30" s="8" t="n">
-        <v>2.920932025944726</v>
+        <v>13.60475860726781</v>
       </c>
       <c r="U30" s="8" t="n">
-        <v>0.7559322462129708</v>
+        <v>0.9026515393644193</v>
       </c>
       <c r="V30" s="8" t="n">
-        <v>31.80427743851582</v>
+        <v>20.78360873982991</v>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X30" s="8" t="n">
-        <v>45.20331981413339</v>
+        <v>74.89878097875199</v>
       </c>
       <c r="Y30" s="8" t="n">
-        <v>68.95850406340263</v>
+        <v>77.73441847475044</v>
       </c>
       <c r="Z30" s="8" t="n">
-        <v>-12.55250000113575</v>
+        <v>0.9206836258860873</v>
       </c>
       <c r="AA30" s="8" t="n">
-        <v>15.32745092836607</v>
+        <v>16.73493687825342</v>
       </c>
       <c r="AB30" s="8" t="n">
-        <v>15.29511264379264</v>
+        <v>15.66558728070908</v>
       </c>
       <c r="AC30" s="8" t="n">
-        <v>57.06202598117125</v>
+        <v>42.76573761716853</v>
       </c>
       <c r="AD30" s="8" t="n">
-        <v>-15.9143157631585</v>
+        <v>-2.20588235294118</v>
       </c>
       <c r="AE30" s="8" t="n">
-        <v>-15.9143157631585</v>
+        <v>-5.29763764744332</v>
       </c>
       <c r="AF30" s="8" t="n">
-        <v>7.409314428567959</v>
+        <v>7.808609839960412</v>
       </c>
       <c r="AG30" s="6" t="inlineStr">
         <is>
@@ -10145,12 +10419,22 @@
       <c r="AI30" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="6" t="inlineStr"/>
+      <c r="AJ30" s="5" t="n">
+        <v>1538.0683776</v>
+      </c>
+      <c r="AK30" s="8" t="n">
+        <v>18.600368</v>
+      </c>
       <c r="AL30" s="6" t="inlineStr"/>
-      <c r="AM30" s="6" t="inlineStr"/>
-      <c r="AN30" s="6" t="inlineStr"/>
-      <c r="AO30" s="6" t="inlineStr"/>
+      <c r="AM30" s="8" t="n">
+        <v>0.20311</v>
+      </c>
+      <c r="AN30" s="8" t="n">
+        <v>82.19999999999999</v>
+      </c>
+      <c r="AO30" s="8" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -10158,58 +10442,58 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>AVTNPL</t>
+          <t>SVLL</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>99.75</v>
+        <v>867.9500122070312</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>92.52507767985948</v>
+        <v>823.0891609944509</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>87.3588190137459</v>
+        <v>796.4956140732484</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>75.69815982874651</v>
+        <v>711.5416788454323</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>63.0830508635324</v>
+        <v>63.18625963412578</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.734269495025188</v>
+        <v>12.26574788711923</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.01094510136765</v>
+        <v>9.399876138532498</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.723324393657538</v>
+        <v>2.865871748586734</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>25.83437251493751</v>
+        <v>27.81163412787848</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>30.14710669262487</v>
+        <v>22.69188354879885</v>
       </c>
       <c r="O31" s="8" t="n">
-        <v>15.55463748710342</v>
+        <v>22.34957635976134</v>
       </c>
       <c r="P31" s="9" t="n">
-        <v>5.828997856599047</v>
+        <v>41.43842346617464</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>5.843606873783505</v>
+        <v>4.774286869448234</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>1.48474111643167</v>
+        <v>1.06633174331509</v>
       </c>
       <c r="S31" s="6" t="inlineStr">
         <is>
@@ -10217,13 +10501,13 @@
         </is>
       </c>
       <c r="T31" s="8" t="n">
-        <v>13.60475860726781</v>
+        <v>4.089242053789731</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>0.902651539364527</v>
+        <v>0.9513382141275677</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>20.78360873982435</v>
+        <v>11.25534254575751</v>
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
@@ -10231,31 +10515,31 @@
         </is>
       </c>
       <c r="X31" s="8" t="n">
-        <v>74.89878097875199</v>
+        <v>94.3145259734123</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>77.73441847475044</v>
+        <v>81.01591158084118</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>0.9206836258860873</v>
+        <v>1.55025152811048</v>
       </c>
       <c r="AA31" s="8" t="n">
-        <v>16.73493687825342</v>
+        <v>8.317736856284942</v>
       </c>
       <c r="AB31" s="8" t="n">
-        <v>15.66558728070908</v>
+        <v>9.811486006779656</v>
       </c>
       <c r="AC31" s="8" t="n">
-        <v>42.76573761716853</v>
+        <v>22.27231697663889</v>
       </c>
       <c r="AD31" s="8" t="n">
-        <v>-2.20588235294118</v>
+        <v>-3.022345004800975</v>
       </c>
       <c r="AE31" s="8" t="n">
-        <v>-5.29763764744332</v>
+        <v>-3.287091158141819</v>
       </c>
       <c r="AF31" s="8" t="n">
-        <v>7.808609839960412</v>
+        <v>5.45030275436742</v>
       </c>
       <c r="AG31" s="6" t="inlineStr">
         <is>
@@ -10268,12 +10552,22 @@
       <c r="AI31" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="6" t="inlineStr"/>
+      <c r="AJ31" s="5" t="n">
+        <v>1013.1122176</v>
+      </c>
+      <c r="AK31" s="8" t="n">
+        <v>143.79282</v>
+      </c>
       <c r="AL31" s="6" t="inlineStr"/>
-      <c r="AM31" s="6" t="inlineStr"/>
-      <c r="AN31" s="6" t="inlineStr"/>
-      <c r="AO31" s="6" t="inlineStr"/>
+      <c r="AM31" s="8" t="n">
+        <v>5.09488</v>
+      </c>
+      <c r="AN31" s="8" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="AO31" s="8" t="n">
+        <v>74.09999999999999</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -10281,7 +10575,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>MAGADSUGAR</t>
+          <t>TEXINFRA</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -10290,49 +10584,49 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>602.1500244140625</v>
+        <v>123.9800033569336</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>559.7618682328607</v>
+        <v>119.1175222236475</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>543.6522559905849</v>
+        <v>115.9315833634613</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>514.4415641210097</v>
+        <v>107.59327087597</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>60.99702355789643</v>
+        <v>59.47946329370782</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>14.58884803202272</v>
+        <v>1.870559550670066</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>6.821296940010513</v>
+        <v>1.693048044028185</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>7.767551092012211</v>
+        <v>0.1775115066418813</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>26.98687608624708</v>
+        <v>26.3544226690262</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>30.62519792500175</v>
+        <v>31.44210907696054</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>15.08137344731378</v>
+        <v>15.27102892926532</v>
       </c>
       <c r="P32" s="9" t="n">
-        <v>30.82707231642576</v>
+        <v>5.309555278858124</v>
       </c>
       <c r="Q32" s="8" t="n">
-        <v>5.119500301676951</v>
+        <v>4.282590042824988</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>1.384160103984141</v>
+        <v>1.393805643299728</v>
       </c>
       <c r="S32" s="6" t="inlineStr">
         <is>
@@ -10340,13 +10634,13 @@
         </is>
       </c>
       <c r="T32" s="8" t="n">
-        <v>3.730547451753846</v>
+        <v>1.108801033720714</v>
       </c>
       <c r="U32" s="8" t="n">
-        <v>0.9031936768082618</v>
+        <v>0.8643724421085509</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>26.32634352756279</v>
+        <v>11.78702891561928</v>
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
@@ -10354,31 +10648,31 @@
         </is>
       </c>
       <c r="X32" s="8" t="n">
-        <v>81.92069863974426</v>
+        <v>71.4368084214514</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>75.64480061002597</v>
+        <v>68.60191048233935</v>
       </c>
       <c r="Z32" s="8" t="n">
-        <v>3.613524755707109</v>
+        <v>0.9033943074298723</v>
       </c>
       <c r="AA32" s="8" t="n">
-        <v>11.73687087299184</v>
+        <v>3.28224126237624</v>
       </c>
       <c r="AB32" s="8" t="n">
-        <v>19.07257462504175</v>
+        <v>8.687651169125953</v>
       </c>
       <c r="AC32" s="8" t="n">
-        <v>20.33373936024203</v>
+        <v>8.91550755946473</v>
       </c>
       <c r="AD32" s="8" t="n">
-        <v>-3.470657871524618</v>
+        <v>-2.377950112650717</v>
       </c>
       <c r="AE32" s="8" t="n">
-        <v>-5.165759061718711</v>
+        <v>-3.854202178309041</v>
       </c>
       <c r="AF32" s="8" t="n">
-        <v>7.572533712419349</v>
+        <v>4.082087204732665</v>
       </c>
       <c r="AG32" s="6" t="inlineStr">
         <is>
@@ -10391,12 +10685,22 @@
       <c r="AI32" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="6" t="inlineStr"/>
+      <c r="AJ32" s="5" t="n">
+        <v>1632.8443904</v>
+      </c>
+      <c r="AK32" s="8" t="n">
+        <v>185.71014</v>
+      </c>
       <c r="AL32" s="6" t="inlineStr"/>
-      <c r="AM32" s="6" t="inlineStr"/>
-      <c r="AN32" s="6" t="inlineStr"/>
-      <c r="AO32" s="6" t="inlineStr"/>
+      <c r="AM32" s="8" t="n">
+        <v>0.02626</v>
+      </c>
+      <c r="AN32" s="8" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="AO32" s="8" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -10404,58 +10708,58 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>SVLL</t>
+          <t>IRISDOREME</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>867.9500122070312</v>
+        <v>63.13000106811523</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>823.0891609944509</v>
+        <v>60.70318419872327</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>796.4956140732484</v>
+        <v>58.29863070736534</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>711.5416788454323</v>
+        <v>47.18215031260463</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>63.18625963412578</v>
+        <v>58.43343321644641</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>12.26574788711923</v>
+        <v>0.0309703138263302</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>9.399876138532498</v>
+        <v>0.3287604379103423</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>2.865871748586734</v>
+        <v>-0.2977901240840121</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>27.81163412787848</v>
+        <v>21.56575419120254</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>22.69188354879885</v>
+        <v>20.06350891307437</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>22.34957635976134</v>
+        <v>13.92219289683933</v>
       </c>
       <c r="P33" s="9" t="n">
-        <v>41.43842346617464</v>
+        <v>3.367831761509347</v>
       </c>
       <c r="Q33" s="8" t="n">
-        <v>4.774286869448234</v>
+        <v>5.334756382905119</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>1.06633174331509</v>
+        <v>2.196919835895545</v>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
@@ -10463,13 +10767,13 @@
         </is>
       </c>
       <c r="T33" s="8" t="n">
-        <v>4.089242053789731</v>
+        <v>2.436522467832499</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>0.9513382141275677</v>
+        <v>0.597901864104635</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>11.25534254575751</v>
+        <v>18.56610110795998</v>
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
@@ -10477,31 +10781,31 @@
         </is>
       </c>
       <c r="X33" s="8" t="n">
-        <v>94.3145259734123</v>
+        <v>60.97070744317296</v>
       </c>
       <c r="Y33" s="8" t="n">
-        <v>81.01591158084118</v>
+        <v>32.47101842387341</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>1.55025152811048</v>
+        <v>5.709979534009069</v>
       </c>
       <c r="AA33" s="8" t="n">
-        <v>8.317736856284942</v>
+        <v>7.528533559135342</v>
       </c>
       <c r="AB33" s="8" t="n">
-        <v>9.811486006779656</v>
+        <v>8.67619366894219</v>
       </c>
       <c r="AC33" s="8" t="n">
-        <v>22.27231697663889</v>
+        <v>34.83554352755374</v>
       </c>
       <c r="AD33" s="8" t="n">
-        <v>-3.022345004800975</v>
+        <v>-7.161763135124655</v>
       </c>
       <c r="AE33" s="8" t="n">
-        <v>-3.287091158141819</v>
+        <v>-7.161763135124655</v>
       </c>
       <c r="AF33" s="8" t="n">
-        <v>5.45030275436742</v>
+        <v>3.997841137043689</v>
       </c>
       <c r="AG33" s="6" t="inlineStr">
         <is>
@@ -10514,12 +10818,22 @@
       <c r="AI33" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="6" t="inlineStr"/>
+      <c r="AJ33" s="5" t="n">
+        <v>1224.5925888</v>
+      </c>
+      <c r="AK33" s="8" t="n">
+        <v>71.488884</v>
+      </c>
       <c r="AL33" s="6" t="inlineStr"/>
-      <c r="AM33" s="6" t="inlineStr"/>
-      <c r="AN33" s="6" t="inlineStr"/>
-      <c r="AO33" s="6" t="inlineStr"/>
+      <c r="AM33" s="8" t="n">
+        <v>0.24205</v>
+      </c>
+      <c r="AN33" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AO33" s="8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -10527,58 +10841,58 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MAGADSUGAR</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>28.1200008392334</v>
+        <v>602.1500244140625</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>25.73615057219811</v>
+        <v>559.7618682328607</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>25.15109377044935</v>
+        <v>543.6522559905849</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>25.55378527770167</v>
+        <v>514.4415641210097</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>64.54859228508229</v>
+        <v>60.99702355789643</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.5824139771664534</v>
+        <v>14.58884803202272</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.3038005503126724</v>
+        <v>6.821296940010513</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.278613426853781</v>
+        <v>7.767551092012211</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>17.2021058428417</v>
+        <v>26.98687608624708</v>
       </c>
       <c r="N34" s="8" t="n">
-        <v>28.8827335612418</v>
+        <v>30.62519792500175</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>13.9199735070297</v>
+        <v>15.08137344731378</v>
       </c>
       <c r="P34" s="9" t="n">
-        <v>1.414562324721991</v>
+        <v>30.82707231642576</v>
       </c>
       <c r="Q34" s="8" t="n">
-        <v>5.030449084298655</v>
+        <v>5.119500301676951</v>
       </c>
       <c r="R34" s="8" t="n">
-        <v>5.300273519141848</v>
+        <v>1.384160103984141</v>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
@@ -10586,13 +10900,13 @@
         </is>
       </c>
       <c r="T34" s="8" t="n">
-        <v>5.172883158410666</v>
+        <v>3.730547451753846</v>
       </c>
       <c r="U34" s="8" t="n">
-        <v>1.097267313378886</v>
+        <v>0.9031936768082618</v>
       </c>
       <c r="V34" s="8" t="n">
-        <v>18.06088225008078</v>
+        <v>26.32634352756279</v>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
@@ -10600,31 +10914,31 @@
         </is>
       </c>
       <c r="X34" s="8" t="n">
-        <v>78.43751182779741</v>
+        <v>81.92069863974426</v>
       </c>
       <c r="Y34" s="8" t="n">
-        <v>77.36349961796834</v>
+        <v>75.64480061002597</v>
       </c>
       <c r="Z34" s="8" t="n">
-        <v>8.112266788866052</v>
+        <v>3.613524755707109</v>
       </c>
       <c r="AA34" s="8" t="n">
-        <v>7.410238775566702</v>
+        <v>11.73687087299184</v>
       </c>
       <c r="AB34" s="8" t="n">
-        <v>17.70615972228875</v>
+        <v>19.07257462504175</v>
       </c>
       <c r="AC34" s="8" t="n">
-        <v>22.26087321405825</v>
+        <v>20.33373936024203</v>
       </c>
       <c r="AD34" s="8" t="n">
-        <v>2.328971279687964</v>
+        <v>-3.470657871524618</v>
       </c>
       <c r="AE34" s="8" t="n">
-        <v>-27.31971610921373</v>
+        <v>-5.165759061718711</v>
       </c>
       <c r="AF34" s="8" t="n">
-        <v>9.262652782310333</v>
+        <v>7.572533712419349</v>
       </c>
       <c r="AG34" s="6" t="inlineStr">
         <is>
@@ -10637,11 +10951,19 @@
       <c r="AI34" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="6" t="inlineStr"/>
+      <c r="AJ34" s="5" t="n">
+        <v>848.5275136</v>
+      </c>
+      <c r="AK34" s="8" t="n">
+        <v>16.615618</v>
+      </c>
       <c r="AL34" s="6" t="inlineStr"/>
-      <c r="AM34" s="6" t="inlineStr"/>
-      <c r="AN34" s="6" t="inlineStr"/>
+      <c r="AM34" s="8" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="AN34" s="8" t="n">
+        <v>-6.800000000000001</v>
+      </c>
       <c r="AO34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
@@ -10650,58 +10972,58 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>IRISDOREME</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>63.13000106811523</v>
+        <v>1154.800048828125</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>60.70318419872327</v>
+        <v>1099.967055056996</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>58.29863070736534</v>
+        <v>1085.187262607509</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>47.18215031260463</v>
+        <v>888.815757103342</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>58.43343321644641</v>
+        <v>58.67222777648303</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.0309703138263302</v>
+        <v>-8.011956614712517</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.3287604379103423</v>
+        <v>-15.23765295720584</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>-0.2977901240840121</v>
+        <v>7.225696342493325</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>21.56575419120254</v>
+        <v>16.28024138279779</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>20.06350891307437</v>
+        <v>25.13148060836416</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>13.92219289683933</v>
+        <v>13.71290402303158</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>3.367831761509347</v>
+        <v>56.09578371435433</v>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>5.334756382905119</v>
+        <v>4.857618751512831</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>2.196919835895545</v>
+        <v>2.170612130550497</v>
       </c>
       <c r="S35" s="6" t="inlineStr">
         <is>
@@ -10709,45 +11031,45 @@
         </is>
       </c>
       <c r="T35" s="8" t="n">
-        <v>2.436522467832499</v>
+        <v>1.089482140650105</v>
       </c>
       <c r="U35" s="8" t="n">
-        <v>0.597901864104635</v>
+        <v>0.9921494363986083</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>18.56610110795998</v>
+        <v>11.35239599506449</v>
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X35" s="8" t="n">
-        <v>60.97070744317296</v>
+        <v>81.27253556782121</v>
       </c>
       <c r="Y35" s="8" t="n">
-        <v>32.47101842387341</v>
+        <v>63.40858272856206</v>
       </c>
       <c r="Z35" s="8" t="n">
-        <v>5.709979534009069</v>
+        <v>3.097944290556343</v>
       </c>
       <c r="AA35" s="8" t="n">
-        <v>7.528533559135342</v>
+        <v>8.92285436833733</v>
       </c>
       <c r="AB35" s="8" t="n">
-        <v>8.67619366894219</v>
+        <v>8.115420522990746</v>
       </c>
       <c r="AC35" s="8" t="n">
-        <v>34.83554352755374</v>
+        <v>25.92743997408537</v>
       </c>
       <c r="AD35" s="8" t="n">
-        <v>-7.161763135124655</v>
+        <v>-2.630687282620148</v>
       </c>
       <c r="AE35" s="8" t="n">
-        <v>-7.161763135124655</v>
+        <v>-13.00290939035256</v>
       </c>
       <c r="AF35" s="8" t="n">
-        <v>3.997841137043689</v>
+        <v>4.984966915057965</v>
       </c>
       <c r="AG35" s="6" t="inlineStr">
         <is>
@@ -10760,12 +11082,22 @@
       <c r="AI35" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="6" t="inlineStr"/>
+      <c r="AJ35" s="5" t="n">
+        <v>1770.0153344</v>
+      </c>
+      <c r="AK35" s="8" t="n">
+        <v>27.760244</v>
+      </c>
       <c r="AL35" s="6" t="inlineStr"/>
-      <c r="AM35" s="6" t="inlineStr"/>
-      <c r="AN35" s="6" t="inlineStr"/>
-      <c r="AO35" s="6" t="inlineStr"/>
+      <c r="AM35" s="8" t="n">
+        <v>0.8372499999999999</v>
+      </c>
+      <c r="AN35" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AO35" s="8" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -10773,7 +11105,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -10782,49 +11114,49 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1154.800048828125</v>
+        <v>1951.900024414062</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>1099.967055056996</v>
+        <v>1861.464943804354</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>1085.187262607509</v>
+        <v>1808.31906105044</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>888.815757103342</v>
+        <v>1632.935206691117</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>58.67222777648303</v>
+        <v>64.31412123403931</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-8.011956614712517</v>
+        <v>27.11839025428321</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>-15.23765295720584</v>
+        <v>10.85001524127279</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>7.225696342493325</v>
+        <v>16.26837501301042</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>16.28024138279779</v>
+        <v>19.68999862120563</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>25.13148060836416</v>
+        <v>19.15446135308533</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>13.71290402303158</v>
+        <v>14.99464596109706</v>
       </c>
       <c r="P36" s="9" t="n">
-        <v>56.09578371435433</v>
+        <v>59.83107604437347</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>4.857618751512831</v>
+        <v>3.065273594754632</v>
       </c>
       <c r="R36" s="8" t="n">
-        <v>2.170612130550497</v>
+        <v>1.007088666597277</v>
       </c>
       <c r="S36" s="6" t="inlineStr">
         <is>
@@ -10832,13 +11164,13 @@
         </is>
       </c>
       <c r="T36" s="8" t="n">
-        <v>1.089482140650105</v>
+        <v>1.650049126725109</v>
       </c>
       <c r="U36" s="8" t="n">
-        <v>0.9921494363986083</v>
+        <v>0.9647892914008656</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>11.35239599506449</v>
+        <v>13.8542550933705</v>
       </c>
       <c r="W36" s="6" t="inlineStr">
         <is>
@@ -10846,31 +11178,31 @@
         </is>
       </c>
       <c r="X36" s="8" t="n">
-        <v>81.27253556782121</v>
+        <v>92.70162274760585</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>63.40858272856206</v>
+        <v>87.70501193886726</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>3.097944290556343</v>
+        <v>0.9098885975110438</v>
       </c>
       <c r="AA36" s="8" t="n">
-        <v>8.92285436833733</v>
+        <v>4.497028690084726</v>
       </c>
       <c r="AB36" s="8" t="n">
-        <v>8.115420522990746</v>
+        <v>10.4828255142783</v>
       </c>
       <c r="AC36" s="8" t="n">
-        <v>25.92743997408537</v>
+        <v>29.70347481966595</v>
       </c>
       <c r="AD36" s="8" t="n">
-        <v>-2.630687282620148</v>
+        <v>-0.918780486595816</v>
       </c>
       <c r="AE36" s="8" t="n">
-        <v>-13.00290939035256</v>
+        <v>-3.428652702946733</v>
       </c>
       <c r="AF36" s="8" t="n">
-        <v>4.984966915057965</v>
+        <v>4.858274710502064</v>
       </c>
       <c r="AG36" s="6" t="inlineStr">
         <is>
@@ -10883,12 +11215,22 @@
       <c r="AI36" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="6" t="inlineStr"/>
+      <c r="AJ36" s="5" t="n">
+        <v>86476.7115264</v>
+      </c>
+      <c r="AK36" s="8" t="n">
+        <v>39.973377</v>
+      </c>
       <c r="AL36" s="6" t="inlineStr"/>
-      <c r="AM36" s="6" t="inlineStr"/>
-      <c r="AN36" s="6" t="inlineStr"/>
-      <c r="AO36" s="6" t="inlineStr"/>
+      <c r="AM36" s="8" t="n">
+        <v>0.07518</v>
+      </c>
+      <c r="AN36" s="8" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="AO36" s="8" t="n">
+        <v>30.9</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -10896,58 +11238,58 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>1951.900024414062</v>
+        <v>4109.10009765625</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>1861.464943804354</v>
+        <v>3975.461342688452</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>1808.3190610494</v>
+        <v>3762.833642279556</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>1632.935205564332</v>
+        <v>2918.157269620501</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>64.31412123403905</v>
+        <v>56.59143028579934</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>27.11839025428367</v>
+        <v>163.7704600830007</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>10.85001524127314</v>
+        <v>124.2019563899221</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>16.26837501301053</v>
+        <v>39.56850369307853</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>19.68999862119611</v>
+        <v>27.25678942630232</v>
       </c>
       <c r="N37" s="8" t="n">
-        <v>19.15446135308565</v>
+        <v>28.48071538589043</v>
       </c>
       <c r="O37" s="8" t="n">
-        <v>14.99464596109754</v>
+        <v>17.14289279108814</v>
       </c>
       <c r="P37" s="9" t="n">
-        <v>59.83107604437373</v>
+        <v>227.2338993950992</v>
       </c>
       <c r="Q37" s="8" t="n">
-        <v>3.065273594754645</v>
+        <v>5.530016159127127</v>
       </c>
       <c r="R37" s="8" t="n">
-        <v>1.007088666597277</v>
+        <v>1.65057826971186</v>
       </c>
       <c r="S37" s="6" t="inlineStr">
         <is>
@@ -10955,45 +11297,45 @@
         </is>
       </c>
       <c r="T37" s="8" t="n">
-        <v>1.650049126725109</v>
+        <v>1.195000104582421</v>
       </c>
       <c r="U37" s="8" t="n">
-        <v>0.9647892914008223</v>
+        <v>0.6932462817655279</v>
       </c>
       <c r="V37" s="8" t="n">
-        <v>13.85425509337179</v>
+        <v>30.41591594970265</v>
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X37" s="8" t="n">
-        <v>92.70162274760585</v>
+        <v>46.6032738010943</v>
       </c>
       <c r="Y37" s="8" t="n">
-        <v>87.70501193886726</v>
+        <v>73.05897362127975</v>
       </c>
       <c r="Z37" s="8" t="n">
-        <v>0.9098885975110438</v>
+        <v>-7.458949206123688</v>
       </c>
       <c r="AA37" s="8" t="n">
-        <v>4.497028690084726</v>
+        <v>3.446456577393264</v>
       </c>
       <c r="AB37" s="8" t="n">
-        <v>10.4828255142783</v>
+        <v>12.16629926280646</v>
       </c>
       <c r="AC37" s="8" t="n">
-        <v>29.70347481966595</v>
+        <v>8.183304551298164</v>
       </c>
       <c r="AD37" s="8" t="n">
-        <v>-0.918780486595816</v>
+        <v>-11.05843944466991</v>
       </c>
       <c r="AE37" s="8" t="n">
-        <v>-3.428652702946733</v>
+        <v>-11.05843944466991</v>
       </c>
       <c r="AF37" s="8" t="n">
-        <v>4.858274710502064</v>
+        <v>3.361591107245498</v>
       </c>
       <c r="AG37" s="6" t="inlineStr">
         <is>
@@ -11006,12 +11348,22 @@
       <c r="AI37" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="6" t="inlineStr"/>
+      <c r="AJ37" s="5" t="n">
+        <v>49830.6875392</v>
+      </c>
+      <c r="AK37" s="8" t="n">
+        <v>98.34463</v>
+      </c>
       <c r="AL37" s="6" t="inlineStr"/>
-      <c r="AM37" s="6" t="inlineStr"/>
-      <c r="AN37" s="6" t="inlineStr"/>
-      <c r="AO37" s="6" t="inlineStr"/>
+      <c r="AM37" s="8" t="n">
+        <v>0.09603999999999999</v>
+      </c>
+      <c r="AN37" s="8" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="AO37" s="8" t="n">
+        <v>303.7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -11019,58 +11371,58 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>4109.10009765625</v>
+        <v>713.25</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>3975.461342688452</v>
+        <v>671.0829582690036</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>3762.833642279556</v>
+        <v>667.8867059765802</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>2918.157269620501</v>
+        <v>662.2599847223005</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>56.59143028579934</v>
+        <v>64.37933294993516</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>163.7704600830007</v>
+        <v>1.72831409938567</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>124.2019563899221</v>
+        <v>-3.750460131606607</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>39.56850369307853</v>
+        <v>5.478774230992277</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>27.25678942630232</v>
+        <v>14.89965877420833</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>28.48071538589043</v>
+        <v>28.03010483274131</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>17.14289279108814</v>
+        <v>15.42832147272419</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>227.2338993950992</v>
+        <v>22.28780278303735</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>5.530016159127127</v>
+        <v>3.124823383531349</v>
       </c>
       <c r="R38" s="8" t="n">
-        <v>1.65057826971186</v>
+        <v>4.913118796071611</v>
       </c>
       <c r="S38" s="6" t="inlineStr">
         <is>
@@ -11078,13 +11430,13 @@
         </is>
       </c>
       <c r="T38" s="8" t="n">
-        <v>1.195000104582421</v>
+        <v>3.63481481226531</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>0.6932462817655279</v>
+        <v>1.118536244428056</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>30.41591594970265</v>
+        <v>10.96385986382416</v>
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
@@ -11092,31 +11444,31 @@
         </is>
       </c>
       <c r="X38" s="8" t="n">
-        <v>46.6032738010943</v>
+        <v>93.16011342314067</v>
       </c>
       <c r="Y38" s="8" t="n">
-        <v>73.05897362127975</v>
+        <v>87.18470066572938</v>
       </c>
       <c r="Z38" s="8" t="n">
-        <v>-7.458949206123688</v>
+        <v>4.781840342184229</v>
       </c>
       <c r="AA38" s="8" t="n">
-        <v>3.446456577393264</v>
+        <v>10.06095416019983</v>
       </c>
       <c r="AB38" s="8" t="n">
-        <v>12.16629926280646</v>
+        <v>5.870563615310553</v>
       </c>
       <c r="AC38" s="8" t="n">
-        <v>8.183304551298164</v>
+        <v>-7.044179415203167</v>
       </c>
       <c r="AD38" s="8" t="n">
-        <v>-11.05843944466991</v>
+        <v>2.18481375358166</v>
       </c>
       <c r="AE38" s="8" t="n">
-        <v>-11.05843944466991</v>
+        <v>-18.81971092426513</v>
       </c>
       <c r="AF38" s="8" t="n">
-        <v>3.361591107245498</v>
+        <v>6.283432057306659</v>
       </c>
       <c r="AG38" s="6" t="inlineStr">
         <is>
@@ -11129,12 +11481,22 @@
       <c r="AI38" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="6" t="inlineStr"/>
+      <c r="AJ38" s="5" t="n">
+        <v>6066.1223424</v>
+      </c>
+      <c r="AK38" s="8" t="n">
+        <v>11.561842</v>
+      </c>
       <c r="AL38" s="6" t="inlineStr"/>
-      <c r="AM38" s="6" t="inlineStr"/>
-      <c r="AN38" s="6" t="inlineStr"/>
-      <c r="AO38" s="6" t="inlineStr"/>
+      <c r="AM38" s="8" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="AN38" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AO38" s="8" t="n">
+        <v>4.100000000000001</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -11142,58 +11504,58 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>RUBYMILLS</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>713.25</v>
+        <v>517.7000122070312</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>671.0829582690036</v>
+        <v>488.4208325540783</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>667.8867059765802</v>
+        <v>447.9283734036396</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>662.2599847223005</v>
+        <v>338.585198999641</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>64.37933294993516</v>
+        <v>60.67278996549893</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>1.72831409938567</v>
+        <v>20.44775600229764</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>-3.750460131606607</v>
+        <v>21.12456158539834</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>5.478774230992277</v>
+        <v>-0.6768055831007018</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>14.89965877420833</v>
+        <v>33.58862248503914</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>28.03010483274131</v>
+        <v>27.75318062114914</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>15.42832147272419</v>
+        <v>8.133375594153934</v>
       </c>
       <c r="P39" s="9" t="n">
-        <v>22.28780278303735</v>
+        <v>36.55999675725867</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>3.124823383531349</v>
+        <v>7.062004229321539</v>
       </c>
       <c r="R39" s="8" t="n">
-        <v>4.913118796071611</v>
+        <v>5.210256081756946</v>
       </c>
       <c r="S39" s="6" t="inlineStr">
         <is>
@@ -11201,45 +11563,45 @@
         </is>
       </c>
       <c r="T39" s="8" t="n">
-        <v>3.63481481226531</v>
+        <v>0.8099400976559222</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>1.118536244428056</v>
+        <v>0.8064787774993368</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>10.96385986382416</v>
+        <v>16.99850226834836</v>
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X39" s="8" t="n">
-        <v>93.16011342314067</v>
+        <v>44.0254340737553</v>
       </c>
       <c r="Y39" s="8" t="n">
-        <v>87.18470066572938</v>
+        <v>66.71374437959189</v>
       </c>
       <c r="Z39" s="8" t="n">
-        <v>4.781840342184229</v>
+        <v>-4.351037005629332</v>
       </c>
       <c r="AA39" s="8" t="n">
-        <v>10.06095416019983</v>
+        <v>6.731270020771207</v>
       </c>
       <c r="AB39" s="8" t="n">
-        <v>5.870563615310553</v>
+        <v>20.37836742351884</v>
       </c>
       <c r="AC39" s="8" t="n">
-        <v>-7.044179415203167</v>
+        <v>29.82067919258611</v>
       </c>
       <c r="AD39" s="8" t="n">
-        <v>2.18481375358166</v>
+        <v>-5.701272822034376</v>
       </c>
       <c r="AE39" s="8" t="n">
-        <v>-18.81971092426513</v>
+        <v>-11.31477306945932</v>
       </c>
       <c r="AF39" s="8" t="n">
-        <v>6.283432057306659</v>
+        <v>5.994662328354128</v>
       </c>
       <c r="AG39" s="6" t="inlineStr">
         <is>
@@ -11252,12 +11614,22 @@
       <c r="AI39" s="8" t="n">
         <v>-4.882615700799143</v>
       </c>
-      <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="6" t="inlineStr"/>
+      <c r="AJ39" s="5" t="n">
+        <v>1725.3367808</v>
+      </c>
+      <c r="AK39" s="8" t="n">
+        <v>39.81096</v>
+      </c>
       <c r="AL39" s="6" t="inlineStr"/>
-      <c r="AM39" s="6" t="inlineStr"/>
-      <c r="AN39" s="6" t="inlineStr"/>
-      <c r="AO39" s="6" t="inlineStr"/>
+      <c r="AM39" s="8" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="AN39" s="8" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AO39" s="8" t="n">
+        <v>-3</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:AO39"/>
